--- a/model/risk-factor-library.xlsx
+++ b/model/risk-factor-library.xlsx
@@ -460,7 +460,7 @@
     <t xml:space="preserve">Structure including a trust, a foundation, a nominee arrangement, or an entity incorporated outside the United Kingdom anywhere in the ownership chain</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3(d) only where nominee shareholders or bearer shares are present</t>
+    <t xml:space="preserve">5.3(d), fired on the whole level; see 5.3(d) and methodology 11.9</t>
   </si>
   <si>
     <t xml:space="preserve">Natural person; no beneficial ownership analysis required</t>
@@ -769,13 +769,13 @@
     <t xml:space="preserve">The customer, a beneficial owner or a person exercising control is a politically exposed person, a family member or a known close associate.</t>
   </si>
   <si>
-    <t xml:space="preserve">The customer or a beneficial owner is established in a jurisdiction identified by FATF as a High-Risk Jurisdiction subject to a Call for Action.</t>
+    <t xml:space="preserve">The customer resides in, holds a second residence in, or sends money to or receives money from a jurisdiction identified by FATF as a High-Risk Jurisdiction subject to a Call for Action. Regulation 33(1)(b) requires enhanced due diligence where the customer is established in such a jurisdiction; the Bank applies the escalator to payment corridors as well, which regulation 33(1) permits because it sets a floor and not a ceiling.</t>
   </si>
   <si>
     <t xml:space="preserve">The customer is a money service business, a trust or company service provider, or a dealer in high-value goods.</t>
   </si>
   <si>
-    <t xml:space="preserve">The ownership structure includes nominee shareholders, bearer shares, or an entity incorporated in a jurisdiction with no accessible beneficial ownership register.</t>
+    <t xml:space="preserve">The ownership structure includes nominee shareholders, bearer shares, or an entity incorporated in a jurisdiction with no accessible beneficial ownership register. Because level 5 of factor C1 covers trusts, nominee arrangements and overseas incorporation together, the recorded level cannot tell those apart; the escalator therefore fires on the whole of C1 level 5. That is deliberately conservative and it is the wrong way round: the fix is to split C1 level 5 so the condition can be evaluated, and that is a library change requiring approval (methodology 11.9).</t>
   </si>
   <si>
     <t xml:space="preserve">Screening returns a confirmed adverse media match relating to financial crime, fraud, bribery, corruption or tax evasion.</t>
@@ -925,7 +925,7 @@
     <t xml:space="preserve">Overall status</t>
   </si>
   <si>
-    <t xml:space="preserve">Checks 11 and 12 matter most. If the lowest achievable score were above 1.00, or the highest below 3.50, a band in the methodology would be unreachable and the model would be broken before a single customer was scored.</t>
+    <t xml:space="preserve">Checks 11 and 12 cannot fail while checks 1 to 3, 9 and 10 pass: if every factor runs from 1 to 5 and the weights sum to 100%, the achievable range is 1.00 to 5.00 by arithmetic. They are kept because they evaluate the aggregation formula itself, so a mistyped range or a transposed weight vector fails here and nowhere else in this workbook. They say nothing about the level definitions. See docs/02-risk-factor-rationale.md, 8.2a.</t>
   </si>
 </sst>
 </file>
@@ -1083,140 +1083,144 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1572,178 +1576,178 @@
   <dimension ref="B2:B38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="104"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="104"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3"/>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3"/>
+      <c r="B15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3"/>
+      <c r="B18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3"/>
+      <c r="B26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="3"/>
+      <c r="B29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="3"/>
+      <c r="B37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1767,164 +1771,164 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D2" s="10" t="n">
         <f aca="false">COUNTIF(Factors!$B$2:$B$21,$A2)</f>
         <v>5</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E2" s="11" t="n">
         <f aca="false">SUMIF(Factors!$B$2:$B$21,$A2,Factors!$D$2:$D$21)</f>
         <v>1</v>
       </c>
-      <c r="F2" s="11" t="str">
+      <c r="F2" s="12" t="str">
         <f aca="false">IF(ROUND($E2,6)=1,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="9" t="n">
         <v>0.25</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" s="10" t="n">
         <f aca="false">COUNTIF(Factors!$B$2:$B$21,$A3)</f>
         <v>3</v>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="E3" s="11" t="n">
         <f aca="false">SUMIF(Factors!$B$2:$B$21,$A3,Factors!$D$2:$D$21)</f>
         <v>1</v>
       </c>
-      <c r="F3" s="11" t="str">
+      <c r="F3" s="12" t="str">
         <f aca="false">IF(ROUND($E3,6)=1,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="10" t="n">
         <f aca="false">COUNTIF(Factors!$B$2:$B$21,$A4)</f>
         <v>4</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="11" t="n">
         <f aca="false">SUMIF(Factors!$B$2:$B$21,$A4,Factors!$D$2:$D$21)</f>
         <v>1</v>
       </c>
-      <c r="F4" s="11" t="str">
+      <c r="F4" s="12" t="str">
         <f aca="false">IF(ROUND($E4,6)=1,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="10" t="n">
         <f aca="false">COUNTIF(Factors!$B$2:$B$21,$A5)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="11" t="n">
         <f aca="false">SUMIF(Factors!$B$2:$B$21,$A5,Factors!$D$2:$D$21)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="11" t="str">
+      <c r="F5" s="12" t="str">
         <f aca="false">IF(ROUND($E5,6)=1,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="10" t="n">
         <f aca="false">COUNTIF(Factors!$B$2:$B$21,$A6)</f>
         <v>5</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <f aca="false">SUMIF(Factors!$B$2:$B$21,$A6,Factors!$D$2:$D$21)</f>
         <v>1</v>
       </c>
-      <c r="F6" s="11" t="str">
+      <c r="F6" s="12" t="str">
         <f aca="false">IF(ROUND($E6,6)=1,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <f aca="false">SUM($C$2:$C$6)</f>
         <v>1</v>
       </c>
-      <c r="F7" s="14" t="str">
+      <c r="F7" s="15" t="str">
         <f aca="false">IF(ROUND($C7,6)=1,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1951,689 +1955,689 @@
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E2" s="18" t="n">
+      <c r="E2" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B2,Categories!$A$2:$A$6,0))*$D2</f>
         <v>0.06</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A2)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A2)*99))</f>
         <v>1</v>
       </c>
-      <c r="G2" s="16" t="n">
+      <c r="G2" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A2)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B3,Categories!$A$2:$A$6,0))*$D3</f>
         <v>0.06</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A3)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A3)*99))</f>
         <v>1</v>
       </c>
-      <c r="G3" s="16" t="n">
+      <c r="G3" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A3)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B4,Categories!$A$2:$A$6,0))*$D4</f>
         <v>0.075</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A4)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A4)*99))</f>
         <v>1</v>
       </c>
-      <c r="G4" s="16" t="n">
+      <c r="G4" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A4)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B5,Categories!$A$2:$A$6,0))*$D5</f>
         <v>0.06</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A5)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A5)*99))</f>
         <v>1</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A5)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>0.15</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B6,Categories!$A$2:$A$6,0))*$D6</f>
         <v>0.045</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A6)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A6)*99))</f>
         <v>1</v>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A6)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B7,Categories!$A$2:$A$6,0))*$D7</f>
         <v>0.1</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A7)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A7)*99))</f>
         <v>1</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A7)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B8,Categories!$A$2:$A$6,0))*$D8</f>
         <v>0.05</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A8)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A8)*99))</f>
         <v>1</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A8)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B9,Categories!$A$2:$A$6,0))*$D9</f>
         <v>0.1</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A9)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A9)*99))</f>
         <v>1</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A9)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>0.35</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B10,Categories!$A$2:$A$6,0))*$D10</f>
         <v>0.07</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A10)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A10)*99))</f>
         <v>1</v>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A10)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B11,Categories!$A$2:$A$6,0))*$D11</f>
         <v>0.05</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A11)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A11)*99))</f>
         <v>1</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A11)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B12,Categories!$A$2:$A$6,0))*$D12</f>
         <v>0.05</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A12)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A12)*99))</f>
         <v>1</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A12)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>0.15</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B13,Categories!$A$2:$A$6,0))*$D13</f>
         <v>0.03</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A13)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A13)*99))</f>
         <v>1</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A13)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="4" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>0.45</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B14,Categories!$A$2:$A$6,0))*$D14</f>
         <v>0.045</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A14)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A14)*99))</f>
         <v>1</v>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A14)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="4" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <v>0.35</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B15,Categories!$A$2:$A$6,0))*$D15</f>
         <v>0.035</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A15)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A15)*99))</f>
         <v>1</v>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G15" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A15)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="4" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B16,Categories!$A$2:$A$6,0))*$D16</f>
         <v>0.02</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A16)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A16)*99))</f>
         <v>1</v>
       </c>
-      <c r="G16" s="16" t="n">
+      <c r="G16" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A16)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="4" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B17,Categories!$A$2:$A$6,0))*$D17</f>
         <v>0.0375</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A17)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A17)*99))</f>
         <v>1</v>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A17)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="4" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B18,Categories!$A$2:$A$6,0))*$D18</f>
         <v>0.045</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A18)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A18)*99))</f>
         <v>1</v>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A18)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="4" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B19,Categories!$A$2:$A$6,0))*$D19</f>
         <v>0.03</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A19)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A19)*99))</f>
         <v>1</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A19)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="4" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <v>0.15</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B20,Categories!$A$2:$A$6,0))*$D20</f>
         <v>0.0225</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A20)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A20)*99))</f>
         <v>1</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A20)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <v>0.1</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="19" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B21,Categories!$A$2:$A$6,0))*$D21</f>
         <v>0.015</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A21)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A21)*99))</f>
         <v>1</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="17" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A21)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="4" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="20" t="n">
         <f aca="false">SUM($E$2:$E$21)</f>
         <v>1</v>
       </c>
@@ -2661,1617 +2665,1617 @@
   <dimension ref="A1:E99"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="3" t="str">
+      <c r="B2" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A2,Factors!$A$2:$A$21,0))</f>
         <v>Customer legal form</v>
       </c>
-      <c r="C2" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="3" t="str">
+      <c r="B3" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A3,Factors!$A$2:$A$21,0))</f>
         <v>Customer legal form</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="3" t="str">
+      <c r="B4" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A4,Factors!$A$2:$A$21,0))</f>
         <v>Customer legal form</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E4" s="3"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="3" t="str">
+      <c r="B5" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A5,Factors!$A$2:$A$21,0))</f>
         <v>Customer legal form</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E5" s="3"/>
+      <c r="E5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="3" t="str">
+      <c r="B6" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A6,Factors!$A$2:$A$21,0))</f>
         <v>Customer legal form</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="3" t="str">
+      <c r="B7" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A7,Factors!$A$2:$A$21,0))</f>
         <v>Ownership and control structure</v>
       </c>
-      <c r="C7" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E7" s="3"/>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="3" t="str">
+      <c r="B8" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A8,Factors!$A$2:$A$21,0))</f>
         <v>Ownership and control structure</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E8" s="3"/>
+      <c r="E8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="3" t="str">
+      <c r="B9" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A9,Factors!$A$2:$A$21,0))</f>
         <v>Ownership and control structure</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="E9" s="3"/>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="3" t="str">
+      <c r="B10" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A10,Factors!$A$2:$A$21,0))</f>
         <v>Ownership and control structure</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="E10" s="3"/>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="3" t="str">
+      <c r="B11" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A11,Factors!$A$2:$A$21,0))</f>
         <v>Ownership and control structure</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="3" t="str">
+      <c r="B12" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A12,Factors!$A$2:$A$21,0))</f>
         <v>Industry or occupation</v>
       </c>
-      <c r="C12" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="C12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="3" t="str">
+      <c r="B13" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A13,Factors!$A$2:$A$21,0))</f>
         <v>Industry or occupation</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E13" s="3"/>
+      <c r="E13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="3" t="str">
+      <c r="B14" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A14,Factors!$A$2:$A$21,0))</f>
         <v>Industry or occupation</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E14" s="3"/>
+      <c r="E14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="3" t="str">
+      <c r="B15" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A15,Factors!$A$2:$A$21,0))</f>
         <v>Industry or occupation</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E15" s="3"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="3" t="str">
+      <c r="B16" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A16,Factors!$A$2:$A$21,0))</f>
         <v>Industry or occupation</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="3" t="str">
+      <c r="B17" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A17,Factors!$A$2:$A$21,0))</f>
         <v>PEP screening outcome</v>
       </c>
-      <c r="C17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="C17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E17" s="3"/>
+      <c r="E17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="3" t="str">
+      <c r="B18" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A18,Factors!$A$2:$A$21,0))</f>
         <v>PEP screening outcome</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="4" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="3" t="str">
+      <c r="B19" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A19,Factors!$A$2:$A$21,0))</f>
         <v>PEP screening outcome</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="3" t="str">
+      <c r="B20" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A20,Factors!$A$2:$A$21,0))</f>
         <v>PEP screening outcome</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="4" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="3" t="str">
+      <c r="B21" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A21,Factors!$A$2:$A$21,0))</f>
         <v>Adverse media screening outcome</v>
       </c>
-      <c r="C21" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="C21" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E21" s="3"/>
+      <c r="E21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="3" t="str">
+      <c r="B22" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A22,Factors!$A$2:$A$21,0))</f>
         <v>Adverse media screening outcome</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E22" s="3"/>
+      <c r="E22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="3" t="str">
+      <c r="B23" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A23,Factors!$A$2:$A$21,0))</f>
         <v>Adverse media screening outcome</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="3"/>
+      <c r="E23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="3" t="str">
+      <c r="B24" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A24,Factors!$A$2:$A$21,0))</f>
         <v>Adverse media screening outcome</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E24" s="3"/>
+      <c r="E24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="3" t="str">
+      <c r="B25" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A25,Factors!$A$2:$A$21,0))</f>
         <v>Adverse media screening outcome</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="4" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="3" t="str">
+      <c r="B26" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A26,Factors!$A$2:$A$21,0))</f>
         <v>Country of residence or incorporation</v>
       </c>
-      <c r="C26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="C26" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E26" s="3"/>
+      <c r="E26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="3" t="str">
+      <c r="B27" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A27,Factors!$A$2:$A$21,0))</f>
         <v>Country of residence or incorporation</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E27" s="3"/>
+      <c r="E27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B28" s="3" t="str">
+      <c r="B28" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A28,Factors!$A$2:$A$21,0))</f>
         <v>Country of residence or incorporation</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E28" s="3"/>
+      <c r="E28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="3" t="str">
+      <c r="B29" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A29,Factors!$A$2:$A$21,0))</f>
         <v>Country of residence or incorporation</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E29" s="3"/>
+      <c r="E29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="3" t="str">
+      <c r="B30" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A30,Factors!$A$2:$A$21,0))</f>
         <v>Country of residence or incorporation</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B31" s="3" t="str">
+      <c r="B31" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A31,Factors!$A$2:$A$21,0))</f>
         <v>Country of tax residence where different</v>
       </c>
-      <c r="C31" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="C31" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E31" s="3"/>
+      <c r="E31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B32" s="3" t="str">
+      <c r="B32" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A32,Factors!$A$2:$A$21,0))</f>
         <v>Country of tax residence where different</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="E32" s="3"/>
+      <c r="E32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="3" t="str">
+      <c r="B33" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A33,Factors!$A$2:$A$21,0))</f>
         <v>Country of tax residence where different</v>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E33" s="3"/>
+      <c r="E33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="3" t="str">
+      <c r="B34" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A34,Factors!$A$2:$A$21,0))</f>
         <v>Country of tax residence where different</v>
       </c>
-      <c r="C34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B35" s="3" t="str">
+      <c r="B35" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A35,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty or payment corridor countries</v>
       </c>
-      <c r="C35" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="C35" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E35" s="3"/>
+      <c r="E35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="3" t="str">
+      <c r="B36" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A36,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty or payment corridor countries</v>
       </c>
-      <c r="C36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="E36" s="3"/>
+      <c r="E36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B37" s="3" t="str">
+      <c r="B37" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A37,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty or payment corridor countries</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E37" s="3"/>
+      <c r="E37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="3" t="str">
+      <c r="B38" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A38,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty or payment corridor countries</v>
       </c>
-      <c r="C38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="E38" s="3"/>
+      <c r="E38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="3" t="str">
+      <c r="B39" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A39,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty or payment corridor countries</v>
       </c>
-      <c r="C39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="3" t="str">
+      <c r="B40" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A40,Factors!$A$2:$A$21,0))</f>
         <v>Product type held</v>
       </c>
-      <c r="C40" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="3" t="s">
+      <c r="C40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E40" s="3"/>
+      <c r="E40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="3" t="str">
+      <c r="B41" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A41,Factors!$A$2:$A$21,0))</f>
         <v>Product type held</v>
       </c>
-      <c r="C41" s="16" t="n">
+      <c r="C41" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="E41" s="3"/>
+      <c r="E41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="3" t="str">
+      <c r="B42" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A42,Factors!$A$2:$A$21,0))</f>
         <v>Product type held</v>
       </c>
-      <c r="C42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="E42" s="3"/>
+      <c r="E42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B43" s="3" t="str">
+      <c r="B43" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A43,Factors!$A$2:$A$21,0))</f>
         <v>Product type held</v>
       </c>
-      <c r="C43" s="16" t="n">
+      <c r="C43" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E43" s="3"/>
+      <c r="E43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B44" s="3" t="str">
+      <c r="B44" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A44,Factors!$A$2:$A$21,0))</f>
         <v>Product type held</v>
       </c>
-      <c r="C44" s="16" t="n">
+      <c r="C44" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E44" s="3"/>
+      <c r="E44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B45" s="3" t="str">
+      <c r="B45" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A45,Factors!$A$2:$A$21,0))</f>
         <v>Cash functionality</v>
       </c>
-      <c r="C45" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="3" t="s">
+      <c r="C45" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="E45" s="3"/>
+      <c r="E45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="3" t="str">
+      <c r="B46" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A46,Factors!$A$2:$A$21,0))</f>
         <v>Cash functionality</v>
       </c>
-      <c r="C46" s="16" t="n">
+      <c r="C46" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E46" s="3"/>
+      <c r="E46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="3" t="str">
+      <c r="B47" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A47,Factors!$A$2:$A$21,0))</f>
         <v>Cash functionality</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E47" s="3"/>
+      <c r="E47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="3" t="str">
+      <c r="B48" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A48,Factors!$A$2:$A$21,0))</f>
         <v>Cash functionality</v>
       </c>
-      <c r="C48" s="16" t="n">
+      <c r="C48" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E48" s="3"/>
+      <c r="E48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B49" s="3" t="str">
+      <c r="B49" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A49,Factors!$A$2:$A$21,0))</f>
         <v>Cash functionality</v>
       </c>
-      <c r="C49" s="16" t="n">
+      <c r="C49" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="3"/>
+      <c r="E49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B50" s="3" t="str">
+      <c r="B50" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A50,Factors!$A$2:$A$21,0))</f>
         <v>International payment functionality</v>
       </c>
-      <c r="C50" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="3" t="s">
+      <c r="C50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E50" s="3"/>
+      <c r="E50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="3" t="str">
+      <c r="B51" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A51,Factors!$A$2:$A$21,0))</f>
         <v>International payment functionality</v>
       </c>
-      <c r="C51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E51" s="3"/>
+      <c r="E51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B52" s="3" t="str">
+      <c r="B52" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A52,Factors!$A$2:$A$21,0))</f>
         <v>International payment functionality</v>
       </c>
-      <c r="C52" s="16" t="n">
+      <c r="C52" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E52" s="3"/>
+      <c r="E52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B53" s="3" t="str">
+      <c r="B53" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A53,Factors!$A$2:$A$21,0))</f>
         <v>International payment functionality</v>
       </c>
-      <c r="C53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E53" s="3"/>
+      <c r="E53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B54" s="3" t="str">
+      <c r="B54" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A54,Factors!$A$2:$A$21,0))</f>
         <v>International payment functionality</v>
       </c>
-      <c r="C54" s="16" t="n">
+      <c r="C54" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E54" s="3"/>
+      <c r="E54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B55" s="3" t="str">
+      <c r="B55" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A55,Factors!$A$2:$A$21,0))</f>
         <v>Third-party access to the account</v>
       </c>
-      <c r="C55" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="3" t="s">
+      <c r="C55" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E55" s="3"/>
+      <c r="E55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B56" s="3" t="str">
+      <c r="B56" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A56,Factors!$A$2:$A$21,0))</f>
         <v>Third-party access to the account</v>
       </c>
-      <c r="C56" s="16" t="n">
+      <c r="C56" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E56" s="3"/>
+      <c r="E56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B57" s="3" t="str">
+      <c r="B57" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A57,Factors!$A$2:$A$21,0))</f>
         <v>Third-party access to the account</v>
       </c>
-      <c r="C57" s="16" t="n">
+      <c r="C57" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E57" s="3"/>
+      <c r="E57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B58" s="3" t="str">
+      <c r="B58" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A58,Factors!$A$2:$A$21,0))</f>
         <v>Third-party access to the account</v>
       </c>
-      <c r="C58" s="16" t="n">
+      <c r="C58" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E58" s="3"/>
+      <c r="E58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B59" s="3" t="str">
+      <c r="B59" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A59,Factors!$A$2:$A$21,0))</f>
         <v>Third-party access to the account</v>
       </c>
-      <c r="C59" s="16" t="n">
+      <c r="C59" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="E59" s="3"/>
+      <c r="E59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B60" s="3" t="str">
+      <c r="B60" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A60,Factors!$A$2:$A$21,0))</f>
         <v>Onboarding channel</v>
       </c>
-      <c r="C60" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="3" t="s">
+      <c r="C60" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E60" s="3"/>
+      <c r="E60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B61" s="3" t="str">
+      <c r="B61" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A61,Factors!$A$2:$A$21,0))</f>
         <v>Onboarding channel</v>
       </c>
-      <c r="C61" s="16" t="n">
+      <c r="C61" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E61" s="3"/>
+      <c r="E61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B62" s="3" t="str">
+      <c r="B62" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A62,Factors!$A$2:$A$21,0))</f>
         <v>Onboarding channel</v>
       </c>
-      <c r="C62" s="16" t="n">
+      <c r="C62" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="E62" s="3"/>
+      <c r="E62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="12" t="s">
+      <c r="A63" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B63" s="3" t="str">
+      <c r="B63" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A63,Factors!$A$2:$A$21,0))</f>
         <v>Onboarding channel</v>
       </c>
-      <c r="C63" s="16" t="n">
+      <c r="C63" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="E63" s="3"/>
+      <c r="E63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B64" s="3" t="str">
+      <c r="B64" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A64,Factors!$A$2:$A$21,0))</f>
         <v>Onboarding channel</v>
       </c>
-      <c r="C64" s="16" t="n">
+      <c r="C64" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E64" s="3"/>
+      <c r="E64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="12" t="s">
+      <c r="A65" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B65" s="3" t="str">
+      <c r="B65" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A65,Factors!$A$2:$A$21,0))</f>
         <v>Identity verification method</v>
       </c>
-      <c r="C65" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="3" t="s">
+      <c r="C65" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="E65" s="3"/>
+      <c r="E65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B66" s="3" t="str">
+      <c r="B66" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A66,Factors!$A$2:$A$21,0))</f>
         <v>Identity verification method</v>
       </c>
-      <c r="C66" s="16" t="n">
+      <c r="C66" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E66" s="3"/>
+      <c r="E66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B67" s="3" t="str">
+      <c r="B67" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A67,Factors!$A$2:$A$21,0))</f>
         <v>Identity verification method</v>
       </c>
-      <c r="C67" s="16" t="n">
+      <c r="C67" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="E67" s="3"/>
+      <c r="E67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B68" s="3" t="str">
+      <c r="B68" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A68,Factors!$A$2:$A$21,0))</f>
         <v>Identity verification method</v>
       </c>
-      <c r="C68" s="16" t="n">
+      <c r="C68" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E68" s="3"/>
+      <c r="E68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12" t="s">
+      <c r="A69" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B69" s="3" t="str">
+      <c r="B69" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A69,Factors!$A$2:$A$21,0))</f>
         <v>Identity verification method</v>
       </c>
-      <c r="C69" s="16" t="n">
+      <c r="C69" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="E69" s="3"/>
+      <c r="E69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12" t="s">
+      <c r="A70" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B70" s="3" t="str">
+      <c r="B70" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A70,Factors!$A$2:$A$21,0))</f>
         <v>Introduction source</v>
       </c>
-      <c r="C70" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="3" t="s">
+      <c r="C70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="E70" s="3"/>
+      <c r="E70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B71" s="3" t="str">
+      <c r="B71" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A71,Factors!$A$2:$A$21,0))</f>
         <v>Introduction source</v>
       </c>
-      <c r="C71" s="16" t="n">
+      <c r="C71" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E71" s="3"/>
+      <c r="E71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12" t="s">
+      <c r="A72" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B72" s="3" t="str">
+      <c r="B72" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A72,Factors!$A$2:$A$21,0))</f>
         <v>Introduction source</v>
       </c>
-      <c r="C72" s="16" t="n">
+      <c r="C72" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E72" s="3"/>
+      <c r="E72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12" t="s">
+      <c r="A73" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B73" s="3" t="str">
+      <c r="B73" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A73,Factors!$A$2:$A$21,0))</f>
         <v>Introduction source</v>
       </c>
-      <c r="C73" s="16" t="n">
+      <c r="C73" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E73" s="3"/>
+      <c r="E73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12" t="s">
+      <c r="A74" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B74" s="3" t="str">
+      <c r="B74" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A74,Factors!$A$2:$A$21,0))</f>
         <v>Introduction source</v>
       </c>
-      <c r="C74" s="16" t="n">
+      <c r="C74" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="E74" s="3"/>
+      <c r="E74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="12" t="s">
+      <c r="A75" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B75" s="3" t="str">
+      <c r="B75" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A75,Factors!$A$2:$A$21,0))</f>
         <v>Expected turnover relative to declared income</v>
       </c>
-      <c r="C75" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="3" t="s">
+      <c r="C75" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="E75" s="3"/>
+      <c r="E75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="12" t="s">
+      <c r="A76" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B76" s="3" t="str">
+      <c r="B76" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A76,Factors!$A$2:$A$21,0))</f>
         <v>Expected turnover relative to declared income</v>
       </c>
-      <c r="C76" s="16" t="n">
+      <c r="C76" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E76" s="3"/>
+      <c r="E76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="12" t="s">
+      <c r="A77" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B77" s="3" t="str">
+      <c r="B77" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A77,Factors!$A$2:$A$21,0))</f>
         <v>Expected turnover relative to declared income</v>
       </c>
-      <c r="C77" s="16" t="n">
+      <c r="C77" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="E77" s="3"/>
+      <c r="E77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="12" t="s">
+      <c r="A78" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B78" s="3" t="str">
+      <c r="B78" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A78,Factors!$A$2:$A$21,0))</f>
         <v>Expected turnover relative to declared income</v>
       </c>
-      <c r="C78" s="16" t="n">
+      <c r="C78" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E78" s="3"/>
+      <c r="E78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="12" t="s">
+      <c r="A79" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B79" s="3" t="str">
+      <c r="B79" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A79,Factors!$A$2:$A$21,0))</f>
         <v>Expected turnover relative to declared income</v>
       </c>
-      <c r="C79" s="16" t="n">
+      <c r="C79" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="E79" s="3"/>
+      <c r="E79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="12" t="s">
+      <c r="A80" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B80" s="3" t="str">
+      <c r="B80" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A80,Factors!$A$2:$A$21,0))</f>
         <v>Expected cash proportion of credits</v>
       </c>
-      <c r="C80" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="3" t="s">
+      <c r="C80" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E80" s="3"/>
+      <c r="E80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="12" t="s">
+      <c r="A81" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B81" s="3" t="str">
+      <c r="B81" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A81,Factors!$A$2:$A$21,0))</f>
         <v>Expected cash proportion of credits</v>
       </c>
-      <c r="C81" s="16" t="n">
+      <c r="C81" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E81" s="3"/>
+      <c r="E81" s="4"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B82" s="3" t="str">
+      <c r="B82" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A82,Factors!$A$2:$A$21,0))</f>
         <v>Expected cash proportion of credits</v>
       </c>
-      <c r="C82" s="16" t="n">
+      <c r="C82" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E82" s="3"/>
+      <c r="E82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="12" t="s">
+      <c r="A83" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B83" s="3" t="str">
+      <c r="B83" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A83,Factors!$A$2:$A$21,0))</f>
         <v>Expected cash proportion of credits</v>
       </c>
-      <c r="C83" s="16" t="n">
+      <c r="C83" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E83" s="3"/>
+      <c r="E83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="12" t="s">
+      <c r="A84" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B84" s="3" t="str">
+      <c r="B84" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A84,Factors!$A$2:$A$21,0))</f>
         <v>Expected cash proportion of credits</v>
       </c>
-      <c r="C84" s="16" t="n">
+      <c r="C84" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E84" s="3"/>
+      <c r="E84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="12" t="s">
+      <c r="A85" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B85" s="3" t="str">
+      <c r="B85" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A85,Factors!$A$2:$A$21,0))</f>
         <v>Expected international proportion of value</v>
       </c>
-      <c r="C85" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" s="3" t="s">
+      <c r="C85" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="E85" s="3"/>
+      <c r="E85" s="4"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="12" t="s">
+      <c r="A86" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B86" s="3" t="str">
+      <c r="B86" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A86,Factors!$A$2:$A$21,0))</f>
         <v>Expected international proportion of value</v>
       </c>
-      <c r="C86" s="16" t="n">
+      <c r="C86" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="E86" s="3"/>
+      <c r="E86" s="4"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B87" s="3" t="str">
+      <c r="B87" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A87,Factors!$A$2:$A$21,0))</f>
         <v>Expected international proportion of value</v>
       </c>
-      <c r="C87" s="16" t="n">
+      <c r="C87" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="E87" s="3"/>
+      <c r="E87" s="4"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="12" t="s">
+      <c r="A88" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B88" s="3" t="str">
+      <c r="B88" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A88,Factors!$A$2:$A$21,0))</f>
         <v>Expected international proportion of value</v>
       </c>
-      <c r="C88" s="16" t="n">
+      <c r="C88" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="E88" s="3"/>
+      <c r="E88" s="4"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="12" t="s">
+      <c r="A89" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B89" s="3" t="str">
+      <c r="B89" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A89,Factors!$A$2:$A$21,0))</f>
         <v>Expected international proportion of value</v>
       </c>
-      <c r="C89" s="16" t="n">
+      <c r="C89" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E89" s="3"/>
+      <c r="E89" s="4"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="12" t="s">
+      <c r="A90" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B90" s="3" t="str">
+      <c r="B90" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A90,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty profile</v>
       </c>
-      <c r="C90" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" s="3" t="s">
+      <c r="C90" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E90" s="3"/>
+      <c r="E90" s="4"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="12" t="s">
+      <c r="A91" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B91" s="3" t="str">
+      <c r="B91" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A91,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty profile</v>
       </c>
-      <c r="C91" s="16" t="n">
+      <c r="C91" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E91" s="3"/>
+      <c r="E91" s="4"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="12" t="s">
+      <c r="A92" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B92" s="3" t="str">
+      <c r="B92" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A92,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty profile</v>
       </c>
-      <c r="C92" s="16" t="n">
+      <c r="C92" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="E92" s="3"/>
+      <c r="E92" s="4"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="12" t="s">
+      <c r="A93" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B93" s="3" t="str">
+      <c r="B93" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A93,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty profile</v>
       </c>
-      <c r="C93" s="16" t="n">
+      <c r="C93" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E93" s="3"/>
+      <c r="E93" s="4"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="12" t="s">
+      <c r="A94" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B94" s="3" t="str">
+      <c r="B94" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A94,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty profile</v>
       </c>
-      <c r="C94" s="16" t="n">
+      <c r="C94" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E94" s="3"/>
+      <c r="E94" s="4"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="12" t="s">
+      <c r="A95" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B95" s="3" t="str">
+      <c r="B95" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A95,Factors!$A$2:$A$21,0))</f>
         <v>Plausibility of the declared profile</v>
       </c>
-      <c r="C95" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" s="3" t="s">
+      <c r="C95" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="E95" s="3"/>
+      <c r="E95" s="4"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="12" t="s">
+      <c r="A96" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B96" s="3" t="str">
+      <c r="B96" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A96,Factors!$A$2:$A$21,0))</f>
         <v>Plausibility of the declared profile</v>
       </c>
-      <c r="C96" s="16" t="n">
+      <c r="C96" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E96" s="3"/>
+      <c r="E96" s="4"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="12" t="s">
+      <c r="A97" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B97" s="3" t="str">
+      <c r="B97" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A97,Factors!$A$2:$A$21,0))</f>
         <v>Plausibility of the declared profile</v>
       </c>
-      <c r="C97" s="16" t="n">
+      <c r="C97" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E97" s="3"/>
+      <c r="E97" s="4"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="12" t="s">
+      <c r="A98" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B98" s="3" t="str">
+      <c r="B98" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A98,Factors!$A$2:$A$21,0))</f>
         <v>Plausibility of the declared profile</v>
       </c>
-      <c r="C98" s="16" t="n">
+      <c r="C98" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E98" s="3"/>
+      <c r="E98" s="4"/>
     </row>
     <row r="99" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="12" t="s">
+      <c r="A99" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B99" s="3" t="str">
+      <c r="B99" s="4" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A99,Factors!$A$2:$A$21,0))</f>
         <v>Plausibility of the declared profile</v>
       </c>
-      <c r="C99" s="16" t="n">
+      <c r="C99" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E99" s="3"/>
+      <c r="E99" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4296,145 +4300,145 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="116"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="116"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+    <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+    <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>264</v>
       </c>
     </row>
@@ -4461,685 +4465,685 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>266</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J4" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="K4" s="25" t="s">
+      <c r="K4" s="26" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="20" t="str">
+      <c r="B5" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A5,Factors!$A$2:$A$21,0))</f>
         <v>Customer legal form</v>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A5,Factors!$A$2:$A$21,0))</f>
         <v>0.06</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="28" t="n">
         <f aca="false">$D5*$C5</f>
         <v>0.12</v>
       </c>
-      <c r="F5" s="3" t="str">
+      <c r="F5" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A5)*(Levels!$C$2:$C$99=$C5),0),0))</f>
         <v>Joint personal account between parties with an evidenced relationship, or a UK-registered sole trader</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="28" t="n">
+      <c r="J5" s="29" t="n">
         <f aca="false">SUMPRODUCT((Factors!$B$2:$B$21=$H5)*Factors!$D$2:$D$21*$C$5:$C$24)</f>
         <v>1.95</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="K5" s="11" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($H5,Categories!$A$2:$A$6,0))</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="20" t="str">
+      <c r="B6" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A6,Factors!$A$2:$A$21,0))</f>
         <v>Ownership and control structure</v>
       </c>
-      <c r="C6" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="18" t="n">
+      <c r="C6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A6,Factors!$A$2:$A$21,0))</f>
         <v>0.06</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="28" t="n">
         <f aca="false">$D6*$C6</f>
         <v>0.06</v>
       </c>
-      <c r="F6" s="3" t="str">
+      <c r="F6" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A6)*(Levels!$C$2:$C$99=$C6),0),0))</f>
         <v>Natural person; no beneficial ownership analysis required</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="28" t="n">
+      <c r="J6" s="29" t="n">
         <f aca="false">SUMPRODUCT((Factors!$B$2:$B$21=$H6)*Factors!$D$2:$D$21*$C$5:$C$24)</f>
         <v>1</v>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="K6" s="11" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($H6,Categories!$A$2:$A$6,0))</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="20" t="str">
+      <c r="B7" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A7,Factors!$A$2:$A$21,0))</f>
         <v>Industry or occupation</v>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A7,Factors!$A$2:$A$21,0))</f>
         <v>0.075</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="28" t="n">
         <f aca="false">$D7*$C7</f>
         <v>0.3</v>
       </c>
-      <c r="F7" s="3" t="str">
+      <c r="F7" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A7)*(Levels!$C$2:$C$99=$C7),0),0))</f>
         <v>Cash-intensive trade or another sector treated as vulnerable, including used vehicle sales, scrap metal, car washes, takeaways, personal care premises, accountancy practices and registered cryptoasset businesses</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="28" t="n">
+      <c r="J7" s="29" t="n">
         <f aca="false">SUMPRODUCT((Factors!$B$2:$B$21=$H7)*Factors!$D$2:$D$21*$C$5:$C$24)</f>
         <v>3.05</v>
       </c>
-      <c r="K7" s="10" t="n">
+      <c r="K7" s="11" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($H7,Categories!$A$2:$A$6,0))</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="20" t="str">
+      <c r="B8" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A8,Factors!$A$2:$A$21,0))</f>
         <v>PEP screening outcome</v>
       </c>
-      <c r="C8" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="18" t="n">
+      <c r="C8" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A8,Factors!$A$2:$A$21,0))</f>
         <v>0.06</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="28" t="n">
         <f aca="false">$D8*$C8</f>
         <v>0.06</v>
       </c>
-      <c r="F8" s="3" t="str">
+      <c r="F8" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A8)*(Levels!$C$2:$C$99=$C8),0),0))</f>
         <v>No match</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="28" t="n">
+      <c r="J8" s="29" t="n">
         <f aca="false">SUMPRODUCT((Factors!$B$2:$B$21=$H8)*Factors!$D$2:$D$21*$C$5:$C$24)</f>
         <v>2.6</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="K8" s="11" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($H8,Categories!$A$2:$A$6,0))</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="20" t="str">
+      <c r="B9" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A9,Factors!$A$2:$A$21,0))</f>
         <v>Adverse media screening outcome</v>
       </c>
-      <c r="C9" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="18" t="n">
+      <c r="C9" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A9,Factors!$A$2:$A$21,0))</f>
         <v>0.045</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="28" t="n">
         <f aca="false">$D9*$C9</f>
         <v>0.045</v>
       </c>
-      <c r="F9" s="3" t="str">
+      <c r="F9" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A9)*(Levels!$C$2:$C$99=$C9),0),0))</f>
         <v>No match</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="28" t="n">
+      <c r="J9" s="29" t="n">
         <f aca="false">SUMPRODUCT((Factors!$B$2:$B$21=$H9)*Factors!$D$2:$D$21*$C$5:$C$24)</f>
         <v>2.45</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" s="11" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($H9,Categories!$A$2:$A$6,0))</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="20" t="str">
+      <c r="B10" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A10,Factors!$A$2:$A$21,0))</f>
         <v>Country of residence or incorporation</v>
       </c>
-      <c r="C10" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="18" t="n">
+      <c r="C10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A10,Factors!$A$2:$A$21,0))</f>
         <v>0.1</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="28" t="n">
         <f aca="false">$D10*$C10</f>
         <v>0.1</v>
       </c>
-      <c r="F10" s="3" t="str">
+      <c r="F10" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A10)*(Levels!$C$2:$C$99=$C10),0),0))</f>
         <v>United Kingdom</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="20" t="str">
+      <c r="B11" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A11,Factors!$A$2:$A$21,0))</f>
         <v>Country of tax residence where different</v>
       </c>
-      <c r="C11" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="18" t="n">
+      <c r="C11" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A11,Factors!$A$2:$A$21,0))</f>
         <v>0.05</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="28" t="n">
         <f aca="false">$D11*$C11</f>
         <v>0.05</v>
       </c>
-      <c r="F11" s="3" t="str">
+      <c r="F11" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A11)*(Levels!$C$2:$C$99=$C11),0),0))</f>
         <v>No tax residence declared other than the United Kingdom</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="20" t="str">
+      <c r="B12" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A12,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty or payment corridor countries</v>
       </c>
-      <c r="C12" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="18" t="n">
+      <c r="C12" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A12,Factors!$A$2:$A$21,0))</f>
         <v>0.1</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="28" t="n">
         <f aca="false">$D12*$C12</f>
         <v>0.1</v>
       </c>
-      <c r="F12" s="3" t="str">
+      <c r="F12" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A12)*(Levels!$C$2:$C$99=$C12),0),0))</f>
         <v>United Kingdom only</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="20" t="str">
+      <c r="B13" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A13,Factors!$A$2:$A$21,0))</f>
         <v>Product type held</v>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A13,Factors!$A$2:$A$21,0))</f>
         <v>0.07</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="28" t="n">
         <f aca="false">$D13*$C13</f>
         <v>0.28</v>
       </c>
-      <c r="F13" s="3" t="str">
+      <c r="F13" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A13)*(Levels!$C$2:$C$99=$C13),0),0))</f>
         <v>Business current account without cash handling or international payments</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="20" t="str">
+      <c r="B14" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A14,Factors!$A$2:$A$21,0))</f>
         <v>Cash functionality</v>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A14,Factors!$A$2:$A$21,0))</f>
         <v>0.05</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="28" t="n">
         <f aca="false">$D14*$C14</f>
         <v>0.25</v>
       </c>
-      <c r="F14" s="3" t="str">
+      <c r="F14" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A14)*(Levels!$C$2:$C$99=$C14),0),0))</f>
         <v>Cash deposits expected above GBP 10,000 a month, or use of a cash collection service</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="20" t="str">
+      <c r="B15" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A15,Factors!$A$2:$A$21,0))</f>
         <v>International payment functionality</v>
       </c>
-      <c r="C15" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="18" t="n">
+      <c r="C15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A15,Factors!$A$2:$A$21,0))</f>
         <v>0.05</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="28" t="n">
         <f aca="false">$D15*$C15</f>
         <v>0.05</v>
       </c>
-      <c r="F15" s="3" t="str">
+      <c r="F15" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A15)*(Levels!$C$2:$C$99=$C15),0),0))</f>
         <v>Not enabled on the account</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="20" t="str">
+      <c r="B16" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A16,Factors!$A$2:$A$21,0))</f>
         <v>Third-party access to the account</v>
       </c>
-      <c r="C16" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="18" t="n">
+      <c r="C16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A16,Factors!$A$2:$A$21,0))</f>
         <v>0.03</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="28" t="n">
         <f aca="false">$D16*$C16</f>
         <v>0.03</v>
       </c>
-      <c r="F16" s="3" t="str">
+      <c r="F16" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A16)*(Levels!$C$2:$C$99=$C16),0),0))</f>
         <v>Sole named party, no third-party access</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="20" t="str">
+      <c r="B17" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A17,Factors!$A$2:$A$21,0))</f>
         <v>Onboarding channel</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A17,Factors!$A$2:$A$21,0))</f>
         <v>0.045</v>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="28" t="n">
         <f aca="false">$D17*$C17</f>
         <v>0.135</v>
       </c>
-      <c r="F17" s="3" t="str">
+      <c r="F17" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A17)*(Levels!$C$2:$C$99=$C17),0),0))</f>
         <v>Digital application completed by the customer on the Bank's own app or website</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="20" t="str">
+      <c r="B18" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A18,Factors!$A$2:$A$21,0))</f>
         <v>Identity verification method</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A18,Factors!$A$2:$A$21,0))</f>
         <v>0.035</v>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="28" t="n">
         <f aca="false">$D18*$C18</f>
         <v>0.105</v>
       </c>
-      <c r="F18" s="3" t="str">
+      <c r="F18" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A18)*(Levels!$C$2:$C$99=$C18),0),0))</f>
         <v>Electronic verification returning two or more independent matching sources</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="20" t="str">
+      <c r="B19" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A19,Factors!$A$2:$A$21,0))</f>
         <v>Introduction source</v>
       </c>
-      <c r="C19" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="18" t="n">
+      <c r="C19" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A19,Factors!$A$2:$A$21,0))</f>
         <v>0.02</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="28" t="n">
         <f aca="false">$D19*$C19</f>
         <v>0.02</v>
       </c>
-      <c r="F19" s="3" t="str">
+      <c r="F19" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A19)*(Levels!$C$2:$C$99=$C19),0),0))</f>
         <v>Direct application by the customer</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="20" t="str">
+      <c r="B20" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A20,Factors!$A$2:$A$21,0))</f>
         <v>Expected turnover relative to declared income</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A20,Factors!$A$2:$A$21,0))</f>
         <v>0.0375</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="28" t="n">
         <f aca="false">$D20*$C20</f>
         <v>0.075</v>
       </c>
-      <c r="F20" s="3" t="str">
+      <c r="F20" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A20)*(Levels!$C$2:$C$99=$C20),0),0))</f>
         <v>Consistent with declared income or turnover, GBP 5,000 to GBP 25,000 a month</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="20" t="str">
+      <c r="B21" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A21,Factors!$A$2:$A$21,0))</f>
         <v>Expected cash proportion of credits</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A21,Factors!$A$2:$A$21,0))</f>
         <v>0.045</v>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="28" t="n">
         <f aca="false">$D21*$C21</f>
         <v>0.18</v>
       </c>
-      <c r="F21" s="3" t="str">
+      <c r="F21" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A21)*(Levels!$C$2:$C$99=$C21),0),0))</f>
         <v>Above 30% and up to 60% of expected monthly credits</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B22" s="20" t="str">
+      <c r="B22" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A22,Factors!$A$2:$A$21,0))</f>
         <v>Expected international proportion of value</v>
       </c>
-      <c r="C22" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="18" t="n">
+      <c r="C22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A22,Factors!$A$2:$A$21,0))</f>
         <v>0.03</v>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="28" t="n">
         <f aca="false">$D22*$C22</f>
         <v>0.03</v>
       </c>
-      <c r="F22" s="3" t="str">
+      <c r="F22" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A22)*(Levels!$C$2:$C$99=$C22),0),0))</f>
         <v>No international activity declared</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B23" s="20" t="str">
+      <c r="B23" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A23,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty profile</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="18" t="n">
+      <c r="D23" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A23,Factors!$A$2:$A$21,0))</f>
         <v>0.0225</v>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="28" t="n">
         <f aca="false">$D23*$C23</f>
         <v>0.0675</v>
       </c>
-      <c r="F23" s="3" t="str">
+      <c r="F23" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A23)*(Levels!$C$2:$C$99=$C23),0),0))</f>
         <v>A large number of individual counterparties, consistent with the stated business</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B24" s="20" t="str">
+      <c r="B24" s="21" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A24,Factors!$A$2:$A$21,0))</f>
         <v>Plausibility of the declared profile</v>
       </c>
-      <c r="C24" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="18" t="n">
+      <c r="C24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="19" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A24,Factors!$A$2:$A$21,0))</f>
         <v>0.015</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="28" t="n">
         <f aca="false">$D24*$C24</f>
         <v>0.015</v>
       </c>
-      <c r="F24" s="3" t="str">
+      <c r="F24" s="4" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A24)*(Levels!$C$2:$C$99=$C24),0),0))</f>
         <v>Declared activity is consistent with every other item on file</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="I26" s="29" t="n">
+      <c r="I26" s="30" t="n">
         <f aca="false">SUM($E$5:$E$24)</f>
         <v>2.0725</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="I27" s="30" t="n">
+      <c r="I27" s="31" t="n">
         <f aca="false">ROUND($I26,2)</f>
         <v>2.07</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="I28" s="16" t="str">
+      <c r="I28" s="17" t="str">
         <f aca="false">IF($I27&lt;=2,"Low",IF($I27&lt;=3.49,"Medium","High"))</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="12" t="s">
+      <c r="G29" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="I29" s="26" t="s">
+      <c r="I29" s="27" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="I30" s="31" t="str">
+      <c r="I30" s="32" t="str">
         <f aca="false">IF($I29="Yes","High",$I28)</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G32" s="22" t="s">
+      <c r="G32" s="23" t="s">
         <v>277</v>
       </c>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="23"/>
+      <c r="K32" s="23"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
+      <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5165,307 +5169,307 @@
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="32" t="s">
+      <c r="A5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="33" t="s">
         <v>285</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="10" t="n">
         <f aca="false">ROUND(SUM(Categories!$C$2:$C$6),6)</f>
         <v>1</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="33" t="str">
+      <c r="D5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="34" t="str">
         <f aca="false">IF($C5=$D5,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="33" t="s">
         <v>286</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="10" t="n">
         <f aca="false">SUMPRODUCT(--(ROUND(Categories!$E$2:$E$6,6)&lt;&gt;1))</f>
         <v>0</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="33" t="str">
+      <c r="E6" s="34" t="str">
         <f aca="false">IF($C6=$D6,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="33" t="s">
         <v>287</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="10" t="n">
         <f aca="false">ROUND(SUM(Factors!$E$2:$E$21),6)</f>
         <v>1</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="33" t="str">
+      <c r="D7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="34" t="str">
         <f aca="false">IF($C7=$D7,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="33" t="s">
         <v>288</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="10" t="n">
         <f aca="false">SUMPRODUCT(--(COUNTIF(Factors!$A$2:$A$21,Factors!$A$2:$A$21)&gt;1))</f>
         <v>0</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="33" t="str">
+      <c r="E8" s="34" t="str">
         <f aca="false">IF($C8=$D8,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="33" t="s">
         <v>289</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <f aca="false">SUMPRODUCT(--(COUNTIF(Factors!$A$2:$A$21,Levels!$A$2:$A$99)=0))</f>
         <v>0</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="33" t="str">
+      <c r="E9" s="34" t="str">
         <f aca="false">IF($C9=$D9,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="33" t="s">
         <v>290</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <f aca="false">SUMPRODUCT(--(COUNTIF(Levels!$A$2:$A$99,Factors!$A$2:$A$21)&lt;4))</f>
         <v>0</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="33" t="str">
+      <c r="E10" s="34" t="str">
         <f aca="false">IF($C10=$D10,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <f aca="false">SUMPRODUCT(--((Levels!$C$2:$C$99&lt;1)+(Levels!$C$2:$C$99&gt;5)&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="33" t="str">
+      <c r="E11" s="34" t="str">
         <f aca="false">IF($C11=$D11,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="10" t="n">
         <f aca="false">SUMPRODUCT(--(COUNTIFS(Levels!$A$2:$A$99,Levels!$A$2:$A$99,Levels!$C$2:$C$99,Levels!$C$2:$C$99)&gt;1))</f>
         <v>0</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="33" t="str">
+      <c r="E12" s="34" t="str">
         <f aca="false">IF($C12=$D12,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="10" t="n">
         <f aca="false">SUMPRODUCT(--(Factors!$F$2:$F$21&lt;&gt;1))</f>
         <v>0</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="33" t="str">
+      <c r="E13" s="34" t="str">
         <f aca="false">IF($C13=$D13,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="n">
+      <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="10" t="n">
         <f aca="false">SUMPRODUCT(--(Factors!$G$2:$G$21&lt;&gt;5))</f>
         <v>0</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="33" t="str">
+      <c r="E14" s="34" t="str">
         <f aca="false">IF($C14=$D14,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="10" t="n">
         <f aca="false">ROUND(SUMPRODUCT(Factors!$E$2:$E$21,Factors!$F$2:$F$21),2)</f>
         <v>1</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="33" t="str">
+      <c r="D15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="34" t="str">
         <f aca="false">IF($C15=$D15,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="n">
+      <c r="A16" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="10" t="n">
         <f aca="false">ROUND(SUMPRODUCT(Factors!$E$2:$E$21,Factors!$G$2:$G$21),2)</f>
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="33" t="str">
+      <c r="E16" s="34" t="str">
         <f aca="false">IF($C16=$D16,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="33" t="s">
         <v>297</v>
       </c>
-      <c r="C17" s="28" t="n">
+      <c r="C17" s="29" t="n">
         <f aca="false">ROUND(SUM(Example!$E$5:$E$24),2)</f>
         <v>2.07</v>
       </c>
-      <c r="D17" s="28" t="n">
+      <c r="D17" s="29" t="n">
         <v>2.07</v>
       </c>
-      <c r="E17" s="33" t="str">
+      <c r="E17" s="34" t="str">
         <f aca="false">IF($C17=$D17,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="E19" s="31" t="str">
+      <c r="E19" s="32" t="str">
         <f aca="false">IF(COUNTIF($E$5:$E$17,"CHECK")=0,"ALL OK","FIX")</f>
         <v>ALL OK</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/model/risk-factor-library.xlsx
+++ b/model/risk-factor-library.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Risk factor library</t>
   </si>
   <si>
-    <t xml:space="preserve">Northgate Bank UK Limited (fictional)  |  HND-CRA-002  |  version 0.1 draft  |  September 2026</t>
+    <t xml:space="preserve">Northgate Bank UK Limited (fictional)  |  HND-CRA-002  |  version 0.3 draft  |  September 2026</t>
   </si>
   <si>
     <t xml:space="preserve">What this workbook is</t>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">JMLSG, Guidance for the UK financial sector, Part I, chapters 4 and 5</t>
   </si>
   <si>
-    <t xml:space="preserve">FCA Financial Crime Guide (FCG); FCA FG17/6 on politically exposed persons, as updated by FG25/3 (July 2025)</t>
+    <t xml:space="preserve">FCA Financial Crime Guide (FCG); FCA FG25/3 on politically exposed persons (July 2025), which replaces FG17/6</t>
   </si>
   <si>
     <t xml:space="preserve">HM Treasury and Home Office, National Risk Assessment of Money Laundering and Terrorist Financing 2025 (July 2025)</t>
@@ -502,7 +502,7 @@
     <t xml:space="preserve">No match</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmed match on a family member or known close associate of a domestic PEP</t>
+    <t xml:space="preserve">Confirmed match on a family member or known close associate of a politically exposed person, domestic or foreign</t>
   </si>
   <si>
     <t xml:space="preserve">5.3(a)</t>
@@ -769,7 +769,7 @@
     <t xml:space="preserve">The customer, a beneficial owner or a person exercising control is a politically exposed person, a family member or a known close associate.</t>
   </si>
   <si>
-    <t xml:space="preserve">The customer resides in, holds a second residence in, or sends money to or receives money from a jurisdiction identified by FATF as a High-Risk Jurisdiction subject to a Call for Action. Regulation 33(1)(b) requires enhanced due diligence where the customer is established in such a jurisdiction; the Bank applies the escalator to payment corridors as well, which regulation 33(1) permits because it sets a floor and not a ceiling.</t>
+    <t xml:space="preserve">The customer resides in, has a further tax residence in, or sends money to or receives money from a jurisdiction identified by FATF as a High-Risk Jurisdiction subject to a Call for Action. Regulation 33(1)(b) requires enhanced due diligence where the customer is established in such a jurisdiction; the Bank applies the escalator to payment corridors as well, which regulation 33(1) permits because it sets a floor and not a ceiling.</t>
   </si>
   <si>
     <t xml:space="preserve">The customer is a money service business, a trust or company service provider, or a dealer in high-value goods.</t>
@@ -1083,144 +1083,140 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1576,178 +1572,178 @@
   <dimension ref="B2:B38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="104"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="104"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4"/>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4"/>
+      <c r="B7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4"/>
+      <c r="B18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4"/>
+      <c r="B26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="4"/>
+      <c r="B29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4"/>
+      <c r="B37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="4" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1771,164 +1767,164 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="9" t="n">
         <f aca="false">COUNTIF(Factors!$B$2:$B$21,$A2)</f>
         <v>5</v>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" s="10" t="n">
         <f aca="false">SUMIF(Factors!$B$2:$B$21,$A2,Factors!$D$2:$D$21)</f>
         <v>1</v>
       </c>
-      <c r="F2" s="12" t="str">
+      <c r="F2" s="11" t="str">
         <f aca="false">IF(ROUND($E2,6)=1,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="D3" s="10" t="n">
+      <c r="D3" s="9" t="n">
         <f aca="false">COUNTIF(Factors!$B$2:$B$21,$A3)</f>
         <v>3</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="10" t="n">
         <f aca="false">SUMIF(Factors!$B$2:$B$21,$A3,Factors!$D$2:$D$21)</f>
         <v>1</v>
       </c>
-      <c r="F3" s="12" t="str">
+      <c r="F3" s="11" t="str">
         <f aca="false">IF(ROUND($E3,6)=1,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <f aca="false">COUNTIF(Factors!$B$2:$B$21,$A4)</f>
         <v>4</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="10" t="n">
         <f aca="false">SUMIF(Factors!$B$2:$B$21,$A4,Factors!$D$2:$D$21)</f>
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="str">
+      <c r="F4" s="11" t="str">
         <f aca="false">IF(ROUND($E4,6)=1,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <f aca="false">COUNTIF(Factors!$B$2:$B$21,$A5)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="10" t="n">
         <f aca="false">SUMIF(Factors!$B$2:$B$21,$A5,Factors!$D$2:$D$21)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="12" t="str">
+      <c r="F5" s="11" t="str">
         <f aca="false">IF(ROUND($E5,6)=1,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>0.15</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <f aca="false">COUNTIF(Factors!$B$2:$B$21,$A6)</f>
         <v>5</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <f aca="false">SUMIF(Factors!$B$2:$B$21,$A6,Factors!$D$2:$D$21)</f>
         <v>1</v>
       </c>
-      <c r="F6" s="12" t="str">
+      <c r="F6" s="11" t="str">
         <f aca="false">IF(ROUND($E6,6)=1,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="13" t="n">
         <f aca="false">SUM($C$2:$C$6)</f>
         <v>1</v>
       </c>
-      <c r="F7" s="15" t="str">
+      <c r="F7" s="14" t="str">
         <f aca="false">IF(ROUND($C7,6)=1,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1955,689 +1951,689 @@
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="E2" s="19" t="n">
+      <c r="E2" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B2,Categories!$A$2:$A$6,0))*$D2</f>
         <v>0.06</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A2)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A2)*99))</f>
         <v>1</v>
       </c>
-      <c r="G2" s="17" t="n">
+      <c r="G2" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A2)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B3,Categories!$A$2:$A$6,0))*$D3</f>
         <v>0.06</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A3)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A3)*99))</f>
         <v>1</v>
       </c>
-      <c r="G3" s="17" t="n">
+      <c r="G3" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A3)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="17" t="n">
         <v>0.25</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B4,Categories!$A$2:$A$6,0))*$D4</f>
         <v>0.075</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A4)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A4)*99))</f>
         <v>1</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A4)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B5,Categories!$A$2:$A$6,0))*$D5</f>
         <v>0.06</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A5)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A5)*99))</f>
         <v>1</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A5)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B6,Categories!$A$2:$A$6,0))*$D6</f>
         <v>0.045</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A6)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A6)*99))</f>
         <v>1</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A6)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B7,Categories!$A$2:$A$6,0))*$D7</f>
         <v>0.1</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A7)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A7)*99))</f>
         <v>1</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A7)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B8,Categories!$A$2:$A$6,0))*$D8</f>
         <v>0.05</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A8)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A8)*99))</f>
         <v>1</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A8)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B9,Categories!$A$2:$A$6,0))*$D9</f>
         <v>0.1</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A9)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A9)*99))</f>
         <v>1</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A9)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="17" t="n">
         <v>0.35</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B10,Categories!$A$2:$A$6,0))*$D10</f>
         <v>0.07</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A10)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A10)*99))</f>
         <v>1</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A10)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="17" t="n">
         <v>0.25</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B11,Categories!$A$2:$A$6,0))*$D11</f>
         <v>0.05</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A11)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A11)*99))</f>
         <v>1</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A11)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="17" t="n">
         <v>0.25</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B12,Categories!$A$2:$A$6,0))*$D12</f>
         <v>0.05</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A12)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A12)*99))</f>
         <v>1</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A12)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B13,Categories!$A$2:$A$6,0))*$D13</f>
         <v>0.03</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A13)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A13)*99))</f>
         <v>1</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A13)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="17" t="n">
         <v>0.45</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B14,Categories!$A$2:$A$6,0))*$D14</f>
         <v>0.045</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A14)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A14)*99))</f>
         <v>1</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A14)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="17" t="n">
         <v>0.35</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B15,Categories!$A$2:$A$6,0))*$D15</f>
         <v>0.035</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A15)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A15)*99))</f>
         <v>1</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A15)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="3" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B16,Categories!$A$2:$A$6,0))*$D16</f>
         <v>0.02</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="F16" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A16)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A16)*99))</f>
         <v>1</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A16)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="17" t="n">
         <v>0.25</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B17,Categories!$A$2:$A$6,0))*$D17</f>
         <v>0.0375</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A17)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A17)*99))</f>
         <v>1</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A17)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B18,Categories!$A$2:$A$6,0))*$D18</f>
         <v>0.045</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A18)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A18)*99))</f>
         <v>1</v>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="G18" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A18)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="3" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E19" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B19,Categories!$A$2:$A$6,0))*$D19</f>
         <v>0.03</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A19)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A19)*99))</f>
         <v>1</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A19)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="3" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E20" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B20,Categories!$A$2:$A$6,0))*$D20</f>
         <v>0.0225</v>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F20" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A20)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A20)*99))</f>
         <v>1</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A20)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="3" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="17" t="n">
         <v>0.1</v>
       </c>
-      <c r="E21" s="19" t="n">
+      <c r="E21" s="18" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($B21,Categories!$A$2:$A$6,0))*$D21</f>
         <v>0.015</v>
       </c>
-      <c r="F21" s="17" t="n">
+      <c r="F21" s="16" t="n">
         <f aca="false">SUMPRODUCT(MIN((Levels!$A$2:$A$99=$A21)*Levels!$C$2:$C$99+(Levels!$A$2:$A$99&lt;&gt;$A21)*99))</f>
         <v>1</v>
       </c>
-      <c r="G21" s="17" t="n">
+      <c r="G21" s="16" t="n">
         <f aca="false">SUMPRODUCT(MAX((Levels!$A$2:$A$99=$A21)*Levels!$C$2:$C$99))</f>
         <v>5</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="3" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="20" t="n">
+      <c r="E22" s="19" t="n">
         <f aca="false">SUM($E$2:$E$21)</f>
         <v>1</v>
       </c>
@@ -2665,1617 +2661,1617 @@
   <dimension ref="A1:E99"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="4" t="str">
+      <c r="B2" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A2,Factors!$A$2:$A$21,0))</f>
         <v>Customer legal form</v>
       </c>
-      <c r="C2" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E2" s="4"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="4" t="str">
+      <c r="B3" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A3,Factors!$A$2:$A$21,0))</f>
         <v>Customer legal form</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="4" t="str">
+      <c r="B4" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A4,Factors!$A$2:$A$21,0))</f>
         <v>Customer legal form</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="4" t="str">
+      <c r="B5" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A5,Factors!$A$2:$A$21,0))</f>
         <v>Customer legal form</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="4" t="str">
+      <c r="B6" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A6,Factors!$A$2:$A$21,0))</f>
         <v>Customer legal form</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="4" t="str">
+      <c r="B7" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A7,Factors!$A$2:$A$21,0))</f>
         <v>Ownership and control structure</v>
       </c>
-      <c r="C7" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="4" t="str">
+      <c r="B8" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A8,Factors!$A$2:$A$21,0))</f>
         <v>Ownership and control structure</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="4" t="str">
+      <c r="B9" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A9,Factors!$A$2:$A$21,0))</f>
         <v>Ownership and control structure</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="4" t="str">
+      <c r="B10" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A10,Factors!$A$2:$A$21,0))</f>
         <v>Ownership and control structure</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="4" t="str">
+      <c r="B11" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A11,Factors!$A$2:$A$21,0))</f>
         <v>Ownership and control structure</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="4" t="str">
+      <c r="B12" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A12,Factors!$A$2:$A$21,0))</f>
         <v>Industry or occupation</v>
       </c>
-      <c r="C12" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="C12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="4" t="str">
+      <c r="B13" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A13,Factors!$A$2:$A$21,0))</f>
         <v>Industry or occupation</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="4" t="str">
+      <c r="B14" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A14,Factors!$A$2:$A$21,0))</f>
         <v>Industry or occupation</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="4" t="str">
+      <c r="B15" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A15,Factors!$A$2:$A$21,0))</f>
         <v>Industry or occupation</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="4" t="str">
+      <c r="B16" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A16,Factors!$A$2:$A$21,0))</f>
         <v>Industry or occupation</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="4" t="str">
+      <c r="B17" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A17,Factors!$A$2:$A$21,0))</f>
         <v>PEP screening outcome</v>
       </c>
-      <c r="C17" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="C17" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="4" t="str">
+      <c r="B18" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A18,Factors!$A$2:$A$21,0))</f>
         <v>PEP screening outcome</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="4" t="str">
+      <c r="B19" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A19,Factors!$A$2:$A$21,0))</f>
         <v>PEP screening outcome</v>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="4" t="str">
+      <c r="B20" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A20,Factors!$A$2:$A$21,0))</f>
         <v>PEP screening outcome</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="4" t="str">
+      <c r="B21" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A21,Factors!$A$2:$A$21,0))</f>
         <v>Adverse media screening outcome</v>
       </c>
-      <c r="C21" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="C21" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E21" s="4"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="4" t="str">
+      <c r="B22" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A22,Factors!$A$2:$A$21,0))</f>
         <v>Adverse media screening outcome</v>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C22" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="4" t="str">
+      <c r="B23" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A23,Factors!$A$2:$A$21,0))</f>
         <v>Adverse media screening outcome</v>
       </c>
-      <c r="C23" s="17" t="n">
+      <c r="C23" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="4" t="str">
+      <c r="B24" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A24,Factors!$A$2:$A$21,0))</f>
         <v>Adverse media screening outcome</v>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C24" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E24" s="4"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="4" t="str">
+      <c r="B25" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A25,Factors!$A$2:$A$21,0))</f>
         <v>Adverse media screening outcome</v>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C25" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="4" t="str">
+      <c r="B26" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A26,Factors!$A$2:$A$21,0))</f>
         <v>Country of residence or incorporation</v>
       </c>
-      <c r="C26" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="C26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E26" s="4"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="4" t="str">
+      <c r="B27" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A27,Factors!$A$2:$A$21,0))</f>
         <v>Country of residence or incorporation</v>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C27" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E27" s="4"/>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B28" s="4" t="str">
+      <c r="B28" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A28,Factors!$A$2:$A$21,0))</f>
         <v>Country of residence or incorporation</v>
       </c>
-      <c r="C28" s="17" t="n">
+      <c r="C28" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E28" s="4"/>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="4" t="str">
+      <c r="B29" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A29,Factors!$A$2:$A$21,0))</f>
         <v>Country of residence or incorporation</v>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C29" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E29" s="4"/>
+      <c r="E29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="4" t="str">
+      <c r="B30" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A30,Factors!$A$2:$A$21,0))</f>
         <v>Country of residence or incorporation</v>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C30" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="3" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B31" s="4" t="str">
+      <c r="B31" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A31,Factors!$A$2:$A$21,0))</f>
         <v>Country of tax residence where different</v>
       </c>
-      <c r="C31" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="C31" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E31" s="4"/>
+      <c r="E31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B32" s="4" t="str">
+      <c r="B32" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A32,Factors!$A$2:$A$21,0))</f>
         <v>Country of tax residence where different</v>
       </c>
-      <c r="C32" s="17" t="n">
+      <c r="C32" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E32" s="4"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="4" t="str">
+      <c r="B33" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A33,Factors!$A$2:$A$21,0))</f>
         <v>Country of tax residence where different</v>
       </c>
-      <c r="C33" s="17" t="n">
+      <c r="C33" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E33" s="4"/>
+      <c r="E33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="4" t="str">
+      <c r="B34" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A34,Factors!$A$2:$A$21,0))</f>
         <v>Country of tax residence where different</v>
       </c>
-      <c r="C34" s="17" t="n">
+      <c r="C34" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="3" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B35" s="4" t="str">
+      <c r="B35" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A35,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty or payment corridor countries</v>
       </c>
-      <c r="C35" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="C35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E35" s="4"/>
+      <c r="E35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="4" t="str">
+      <c r="B36" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A36,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty or payment corridor countries</v>
       </c>
-      <c r="C36" s="17" t="n">
+      <c r="C36" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E36" s="4"/>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B37" s="4" t="str">
+      <c r="B37" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A37,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty or payment corridor countries</v>
       </c>
-      <c r="C37" s="17" t="n">
+      <c r="C37" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E37" s="4"/>
+      <c r="E37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="4" t="str">
+      <c r="B38" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A38,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty or payment corridor countries</v>
       </c>
-      <c r="C38" s="17" t="n">
+      <c r="C38" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E38" s="4"/>
+      <c r="E38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="4" t="str">
+      <c r="B39" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A39,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty or payment corridor countries</v>
       </c>
-      <c r="C39" s="17" t="n">
+      <c r="C39" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="3" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="4" t="str">
+      <c r="B40" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A40,Factors!$A$2:$A$21,0))</f>
         <v>Product type held</v>
       </c>
-      <c r="C40" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="4" t="s">
+      <c r="C40" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E40" s="4"/>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="4" t="str">
+      <c r="B41" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A41,Factors!$A$2:$A$21,0))</f>
         <v>Product type held</v>
       </c>
-      <c r="C41" s="17" t="n">
+      <c r="C41" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E41" s="4"/>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="4" t="str">
+      <c r="B42" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A42,Factors!$A$2:$A$21,0))</f>
         <v>Product type held</v>
       </c>
-      <c r="C42" s="17" t="n">
+      <c r="C42" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E42" s="4"/>
+      <c r="E42" s="3"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B43" s="4" t="str">
+      <c r="B43" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A43,Factors!$A$2:$A$21,0))</f>
         <v>Product type held</v>
       </c>
-      <c r="C43" s="17" t="n">
+      <c r="C43" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="E43" s="4"/>
+      <c r="E43" s="3"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B44" s="4" t="str">
+      <c r="B44" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A44,Factors!$A$2:$A$21,0))</f>
         <v>Product type held</v>
       </c>
-      <c r="C44" s="17" t="n">
+      <c r="C44" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E44" s="4"/>
+      <c r="E44" s="3"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B45" s="4" t="str">
+      <c r="B45" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A45,Factors!$A$2:$A$21,0))</f>
         <v>Cash functionality</v>
       </c>
-      <c r="C45" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="C45" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E45" s="4"/>
+      <c r="E45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="4" t="str">
+      <c r="B46" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A46,Factors!$A$2:$A$21,0))</f>
         <v>Cash functionality</v>
       </c>
-      <c r="C46" s="17" t="n">
+      <c r="C46" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E46" s="4"/>
+      <c r="E46" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="4" t="str">
+      <c r="B47" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A47,Factors!$A$2:$A$21,0))</f>
         <v>Cash functionality</v>
       </c>
-      <c r="C47" s="17" t="n">
+      <c r="C47" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E47" s="4"/>
+      <c r="E47" s="3"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="4" t="str">
+      <c r="B48" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A48,Factors!$A$2:$A$21,0))</f>
         <v>Cash functionality</v>
       </c>
-      <c r="C48" s="17" t="n">
+      <c r="C48" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E48" s="4"/>
+      <c r="E48" s="3"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B49" s="4" t="str">
+      <c r="B49" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A49,Factors!$A$2:$A$21,0))</f>
         <v>Cash functionality</v>
       </c>
-      <c r="C49" s="17" t="n">
+      <c r="C49" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="4"/>
+      <c r="E49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B50" s="4" t="str">
+      <c r="B50" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A50,Factors!$A$2:$A$21,0))</f>
         <v>International payment functionality</v>
       </c>
-      <c r="C50" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="4" t="s">
+      <c r="C50" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E50" s="4"/>
+      <c r="E50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="4" t="str">
+      <c r="B51" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A51,Factors!$A$2:$A$21,0))</f>
         <v>International payment functionality</v>
       </c>
-      <c r="C51" s="17" t="n">
+      <c r="C51" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E51" s="4"/>
+      <c r="E51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B52" s="4" t="str">
+      <c r="B52" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A52,Factors!$A$2:$A$21,0))</f>
         <v>International payment functionality</v>
       </c>
-      <c r="C52" s="17" t="n">
+      <c r="C52" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="E52" s="4"/>
+      <c r="E52" s="3"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B53" s="4" t="str">
+      <c r="B53" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A53,Factors!$A$2:$A$21,0))</f>
         <v>International payment functionality</v>
       </c>
-      <c r="C53" s="17" t="n">
+      <c r="C53" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E53" s="4"/>
+      <c r="E53" s="3"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B54" s="4" t="str">
+      <c r="B54" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A54,Factors!$A$2:$A$21,0))</f>
         <v>International payment functionality</v>
       </c>
-      <c r="C54" s="17" t="n">
+      <c r="C54" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E54" s="4"/>
+      <c r="E54" s="3"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B55" s="4" t="str">
+      <c r="B55" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A55,Factors!$A$2:$A$21,0))</f>
         <v>Third-party access to the account</v>
       </c>
-      <c r="C55" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="4" t="s">
+      <c r="C55" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E55" s="4"/>
+      <c r="E55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B56" s="4" t="str">
+      <c r="B56" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A56,Factors!$A$2:$A$21,0))</f>
         <v>Third-party access to the account</v>
       </c>
-      <c r="C56" s="17" t="n">
+      <c r="C56" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E56" s="4"/>
+      <c r="E56" s="3"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B57" s="4" t="str">
+      <c r="B57" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A57,Factors!$A$2:$A$21,0))</f>
         <v>Third-party access to the account</v>
       </c>
-      <c r="C57" s="17" t="n">
+      <c r="C57" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E57" s="4"/>
+      <c r="E57" s="3"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B58" s="4" t="str">
+      <c r="B58" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A58,Factors!$A$2:$A$21,0))</f>
         <v>Third-party access to the account</v>
       </c>
-      <c r="C58" s="17" t="n">
+      <c r="C58" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E58" s="4"/>
+      <c r="E58" s="3"/>
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B59" s="4" t="str">
+      <c r="B59" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A59,Factors!$A$2:$A$21,0))</f>
         <v>Third-party access to the account</v>
       </c>
-      <c r="C59" s="17" t="n">
+      <c r="C59" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E59" s="4"/>
+      <c r="E59" s="3"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B60" s="4" t="str">
+      <c r="B60" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A60,Factors!$A$2:$A$21,0))</f>
         <v>Onboarding channel</v>
       </c>
-      <c r="C60" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="4" t="s">
+      <c r="C60" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E60" s="4"/>
+      <c r="E60" s="3"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B61" s="4" t="str">
+      <c r="B61" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A61,Factors!$A$2:$A$21,0))</f>
         <v>Onboarding channel</v>
       </c>
-      <c r="C61" s="17" t="n">
+      <c r="C61" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E61" s="4"/>
+      <c r="E61" s="3"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B62" s="4" t="str">
+      <c r="B62" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A62,Factors!$A$2:$A$21,0))</f>
         <v>Onboarding channel</v>
       </c>
-      <c r="C62" s="17" t="n">
+      <c r="C62" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E62" s="4"/>
+      <c r="E62" s="3"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B63" s="4" t="str">
+      <c r="B63" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A63,Factors!$A$2:$A$21,0))</f>
         <v>Onboarding channel</v>
       </c>
-      <c r="C63" s="17" t="n">
+      <c r="C63" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E63" s="4"/>
+      <c r="E63" s="3"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B64" s="4" t="str">
+      <c r="B64" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A64,Factors!$A$2:$A$21,0))</f>
         <v>Onboarding channel</v>
       </c>
-      <c r="C64" s="17" t="n">
+      <c r="C64" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E64" s="4"/>
+      <c r="E64" s="3"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B65" s="4" t="str">
+      <c r="B65" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A65,Factors!$A$2:$A$21,0))</f>
         <v>Identity verification method</v>
       </c>
-      <c r="C65" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="4" t="s">
+      <c r="C65" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="E65" s="4"/>
+      <c r="E65" s="3"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B66" s="4" t="str">
+      <c r="B66" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A66,Factors!$A$2:$A$21,0))</f>
         <v>Identity verification method</v>
       </c>
-      <c r="C66" s="17" t="n">
+      <c r="C66" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E66" s="4"/>
+      <c r="E66" s="3"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B67" s="4" t="str">
+      <c r="B67" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A67,Factors!$A$2:$A$21,0))</f>
         <v>Identity verification method</v>
       </c>
-      <c r="C67" s="17" t="n">
+      <c r="C67" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E67" s="4"/>
+      <c r="E67" s="3"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B68" s="4" t="str">
+      <c r="B68" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A68,Factors!$A$2:$A$21,0))</f>
         <v>Identity verification method</v>
       </c>
-      <c r="C68" s="17" t="n">
+      <c r="C68" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E68" s="4"/>
+      <c r="E68" s="3"/>
     </row>
     <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B69" s="4" t="str">
+      <c r="B69" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A69,Factors!$A$2:$A$21,0))</f>
         <v>Identity verification method</v>
       </c>
-      <c r="C69" s="17" t="n">
+      <c r="C69" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E69" s="4"/>
+      <c r="E69" s="3"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B70" s="4" t="str">
+      <c r="B70" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A70,Factors!$A$2:$A$21,0))</f>
         <v>Introduction source</v>
       </c>
-      <c r="C70" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="4" t="s">
+      <c r="C70" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E70" s="4"/>
+      <c r="E70" s="3"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B71" s="4" t="str">
+      <c r="B71" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A71,Factors!$A$2:$A$21,0))</f>
         <v>Introduction source</v>
       </c>
-      <c r="C71" s="17" t="n">
+      <c r="C71" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E71" s="4"/>
+      <c r="E71" s="3"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B72" s="4" t="str">
+      <c r="B72" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A72,Factors!$A$2:$A$21,0))</f>
         <v>Introduction source</v>
       </c>
-      <c r="C72" s="17" t="n">
+      <c r="C72" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E72" s="4"/>
+      <c r="E72" s="3"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B73" s="4" t="str">
+      <c r="B73" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A73,Factors!$A$2:$A$21,0))</f>
         <v>Introduction source</v>
       </c>
-      <c r="C73" s="17" t="n">
+      <c r="C73" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E73" s="4"/>
+      <c r="E73" s="3"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B74" s="4" t="str">
+      <c r="B74" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A74,Factors!$A$2:$A$21,0))</f>
         <v>Introduction source</v>
       </c>
-      <c r="C74" s="17" t="n">
+      <c r="C74" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E74" s="4"/>
+      <c r="E74" s="3"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B75" s="4" t="str">
+      <c r="B75" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A75,Factors!$A$2:$A$21,0))</f>
         <v>Expected turnover relative to declared income</v>
       </c>
-      <c r="C75" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="4" t="s">
+      <c r="C75" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E75" s="4"/>
+      <c r="E75" s="3"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B76" s="4" t="str">
+      <c r="B76" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A76,Factors!$A$2:$A$21,0))</f>
         <v>Expected turnover relative to declared income</v>
       </c>
-      <c r="C76" s="17" t="n">
+      <c r="C76" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E76" s="4"/>
+      <c r="E76" s="3"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B77" s="4" t="str">
+      <c r="B77" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A77,Factors!$A$2:$A$21,0))</f>
         <v>Expected turnover relative to declared income</v>
       </c>
-      <c r="C77" s="17" t="n">
+      <c r="C77" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E77" s="4"/>
+      <c r="E77" s="3"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B78" s="4" t="str">
+      <c r="B78" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A78,Factors!$A$2:$A$21,0))</f>
         <v>Expected turnover relative to declared income</v>
       </c>
-      <c r="C78" s="17" t="n">
+      <c r="C78" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E78" s="4"/>
+      <c r="E78" s="3"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B79" s="4" t="str">
+      <c r="B79" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A79,Factors!$A$2:$A$21,0))</f>
         <v>Expected turnover relative to declared income</v>
       </c>
-      <c r="C79" s="17" t="n">
+      <c r="C79" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E79" s="4"/>
+      <c r="E79" s="3"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B80" s="4" t="str">
+      <c r="B80" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A80,Factors!$A$2:$A$21,0))</f>
         <v>Expected cash proportion of credits</v>
       </c>
-      <c r="C80" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="4" t="s">
+      <c r="C80" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E80" s="4"/>
+      <c r="E80" s="3"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="13" t="s">
+      <c r="A81" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B81" s="4" t="str">
+      <c r="B81" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A81,Factors!$A$2:$A$21,0))</f>
         <v>Expected cash proportion of credits</v>
       </c>
-      <c r="C81" s="17" t="n">
+      <c r="C81" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E81" s="4"/>
+      <c r="E81" s="3"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="13" t="s">
+      <c r="A82" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B82" s="4" t="str">
+      <c r="B82" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A82,Factors!$A$2:$A$21,0))</f>
         <v>Expected cash proportion of credits</v>
       </c>
-      <c r="C82" s="17" t="n">
+      <c r="C82" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E82" s="4"/>
+      <c r="E82" s="3"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B83" s="4" t="str">
+      <c r="B83" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A83,Factors!$A$2:$A$21,0))</f>
         <v>Expected cash proportion of credits</v>
       </c>
-      <c r="C83" s="17" t="n">
+      <c r="C83" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E83" s="4"/>
+      <c r="E83" s="3"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B84" s="4" t="str">
+      <c r="B84" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A84,Factors!$A$2:$A$21,0))</f>
         <v>Expected cash proportion of credits</v>
       </c>
-      <c r="C84" s="17" t="n">
+      <c r="C84" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E84" s="4"/>
+      <c r="E84" s="3"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="13" t="s">
+      <c r="A85" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B85" s="4" t="str">
+      <c r="B85" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A85,Factors!$A$2:$A$21,0))</f>
         <v>Expected international proportion of value</v>
       </c>
-      <c r="C85" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" s="4" t="s">
+      <c r="C85" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="E85" s="4"/>
+      <c r="E85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="13" t="s">
+      <c r="A86" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B86" s="4" t="str">
+      <c r="B86" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A86,Factors!$A$2:$A$21,0))</f>
         <v>Expected international proportion of value</v>
       </c>
-      <c r="C86" s="17" t="n">
+      <c r="C86" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E86" s="4"/>
+      <c r="E86" s="3"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="13" t="s">
+      <c r="A87" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B87" s="4" t="str">
+      <c r="B87" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A87,Factors!$A$2:$A$21,0))</f>
         <v>Expected international proportion of value</v>
       </c>
-      <c r="C87" s="17" t="n">
+      <c r="C87" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E87" s="4"/>
+      <c r="E87" s="3"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B88" s="4" t="str">
+      <c r="B88" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A88,Factors!$A$2:$A$21,0))</f>
         <v>Expected international proportion of value</v>
       </c>
-      <c r="C88" s="17" t="n">
+      <c r="C88" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E88" s="4"/>
+      <c r="E88" s="3"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B89" s="4" t="str">
+      <c r="B89" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A89,Factors!$A$2:$A$21,0))</f>
         <v>Expected international proportion of value</v>
       </c>
-      <c r="C89" s="17" t="n">
+      <c r="C89" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D89" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E89" s="4"/>
+      <c r="E89" s="3"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B90" s="4" t="str">
+      <c r="B90" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A90,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty profile</v>
       </c>
-      <c r="C90" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" s="4" t="s">
+      <c r="C90" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="E90" s="4"/>
+      <c r="E90" s="3"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="13" t="s">
+      <c r="A91" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B91" s="4" t="str">
+      <c r="B91" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A91,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty profile</v>
       </c>
-      <c r="C91" s="17" t="n">
+      <c r="C91" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E91" s="4"/>
+      <c r="E91" s="3"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="13" t="s">
+      <c r="A92" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B92" s="4" t="str">
+      <c r="B92" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A92,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty profile</v>
       </c>
-      <c r="C92" s="17" t="n">
+      <c r="C92" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="E92" s="4"/>
+      <c r="E92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="13" t="s">
+      <c r="A93" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B93" s="4" t="str">
+      <c r="B93" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A93,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty profile</v>
       </c>
-      <c r="C93" s="17" t="n">
+      <c r="C93" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D93" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E93" s="4"/>
+      <c r="E93" s="3"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="13" t="s">
+      <c r="A94" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B94" s="4" t="str">
+      <c r="B94" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A94,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty profile</v>
       </c>
-      <c r="C94" s="17" t="n">
+      <c r="C94" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="D94" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="E94" s="4"/>
+      <c r="E94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="13" t="s">
+      <c r="A95" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B95" s="4" t="str">
+      <c r="B95" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A95,Factors!$A$2:$A$21,0))</f>
         <v>Plausibility of the declared profile</v>
       </c>
-      <c r="C95" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" s="4" t="s">
+      <c r="C95" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E95" s="4"/>
+      <c r="E95" s="3"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="13" t="s">
+      <c r="A96" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B96" s="4" t="str">
+      <c r="B96" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A96,Factors!$A$2:$A$21,0))</f>
         <v>Plausibility of the declared profile</v>
       </c>
-      <c r="C96" s="17" t="n">
+      <c r="C96" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="D96" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E96" s="4"/>
+      <c r="E96" s="3"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="13" t="s">
+      <c r="A97" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B97" s="4" t="str">
+      <c r="B97" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A97,Factors!$A$2:$A$21,0))</f>
         <v>Plausibility of the declared profile</v>
       </c>
-      <c r="C97" s="17" t="n">
+      <c r="C97" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="D97" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E97" s="4"/>
+      <c r="E97" s="3"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="13" t="s">
+      <c r="A98" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B98" s="4" t="str">
+      <c r="B98" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A98,Factors!$A$2:$A$21,0))</f>
         <v>Plausibility of the declared profile</v>
       </c>
-      <c r="C98" s="17" t="n">
+      <c r="C98" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D98" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E98" s="4"/>
+      <c r="E98" s="3"/>
     </row>
     <row r="99" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="13" t="s">
+      <c r="A99" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B99" s="4" t="str">
+      <c r="B99" s="3" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A99,Factors!$A$2:$A$21,0))</f>
         <v>Plausibility of the declared profile</v>
       </c>
-      <c r="C99" s="17" t="n">
+      <c r="C99" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E99" s="4"/>
+      <c r="E99" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4300,145 +4296,145 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="116"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="116"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>264</v>
       </c>
     </row>
@@ -4465,685 +4461,685 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>266</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="12" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="25" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="21" t="str">
+      <c r="B5" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A5,Factors!$A$2:$A$21,0))</f>
         <v>Customer legal form</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A5,Factors!$A$2:$A$21,0))</f>
         <v>0.06</v>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="27" t="n">
         <f aca="false">$D5*$C5</f>
         <v>0.12</v>
       </c>
-      <c r="F5" s="4" t="str">
+      <c r="F5" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A5)*(Levels!$C$2:$C$99=$C5),0),0))</f>
         <v>Joint personal account between parties with an evidenced relationship, or a UK-registered sole trader</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="29" t="n">
+      <c r="J5" s="28" t="n">
         <f aca="false">SUMPRODUCT((Factors!$B$2:$B$21=$H5)*Factors!$D$2:$D$21*$C$5:$C$24)</f>
         <v>1.95</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" s="10" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($H5,Categories!$A$2:$A$6,0))</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="21" t="str">
+      <c r="B6" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A6,Factors!$A$2:$A$21,0))</f>
         <v>Ownership and control structure</v>
       </c>
-      <c r="C6" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="19" t="n">
+      <c r="C6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A6,Factors!$A$2:$A$21,0))</f>
         <v>0.06</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="27" t="n">
         <f aca="false">$D6*$C6</f>
         <v>0.06</v>
       </c>
-      <c r="F6" s="4" t="str">
+      <c r="F6" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A6)*(Levels!$C$2:$C$99=$C6),0),0))</f>
         <v>Natural person; no beneficial ownership analysis required</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="28" t="n">
         <f aca="false">SUMPRODUCT((Factors!$B$2:$B$21=$H6)*Factors!$D$2:$D$21*$C$5:$C$24)</f>
         <v>1</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="10" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($H6,Categories!$A$2:$A$6,0))</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="21" t="str">
+      <c r="B7" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A7,Factors!$A$2:$A$21,0))</f>
         <v>Industry or occupation</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A7,Factors!$A$2:$A$21,0))</f>
         <v>0.075</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="27" t="n">
         <f aca="false">$D7*$C7</f>
         <v>0.3</v>
       </c>
-      <c r="F7" s="4" t="str">
+      <c r="F7" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A7)*(Levels!$C$2:$C$99=$C7),0),0))</f>
         <v>Cash-intensive trade or another sector treated as vulnerable, including used vehicle sales, scrap metal, car washes, takeaways, personal care premises, accountancy practices and registered cryptoasset businesses</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="29" t="n">
+      <c r="J7" s="28" t="n">
         <f aca="false">SUMPRODUCT((Factors!$B$2:$B$21=$H7)*Factors!$D$2:$D$21*$C$5:$C$24)</f>
         <v>3.05</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="10" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($H7,Categories!$A$2:$A$6,0))</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="21" t="str">
+      <c r="B8" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A8,Factors!$A$2:$A$21,0))</f>
         <v>PEP screening outcome</v>
       </c>
-      <c r="C8" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="19" t="n">
+      <c r="C8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A8,Factors!$A$2:$A$21,0))</f>
         <v>0.06</v>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="27" t="n">
         <f aca="false">$D8*$C8</f>
         <v>0.06</v>
       </c>
-      <c r="F8" s="4" t="str">
+      <c r="F8" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A8)*(Levels!$C$2:$C$99=$C8),0),0))</f>
         <v>No match</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="J8" s="28" t="n">
         <f aca="false">SUMPRODUCT((Factors!$B$2:$B$21=$H8)*Factors!$D$2:$D$21*$C$5:$C$24)</f>
         <v>2.6</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="10" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($H8,Categories!$A$2:$A$6,0))</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="21" t="str">
+      <c r="B9" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A9,Factors!$A$2:$A$21,0))</f>
         <v>Adverse media screening outcome</v>
       </c>
-      <c r="C9" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="19" t="n">
+      <c r="C9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A9,Factors!$A$2:$A$21,0))</f>
         <v>0.045</v>
       </c>
-      <c r="E9" s="28" t="n">
+      <c r="E9" s="27" t="n">
         <f aca="false">$D9*$C9</f>
         <v>0.045</v>
       </c>
-      <c r="F9" s="4" t="str">
+      <c r="F9" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A9)*(Levels!$C$2:$C$99=$C9),0),0))</f>
         <v>No match</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="29" t="n">
+      <c r="J9" s="28" t="n">
         <f aca="false">SUMPRODUCT((Factors!$B$2:$B$21=$H9)*Factors!$D$2:$D$21*$C$5:$C$24)</f>
         <v>2.45</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K9" s="10" t="n">
         <f aca="false">INDEX(Categories!$C$2:$C$6,MATCH($H9,Categories!$A$2:$A$6,0))</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="21" t="str">
+      <c r="B10" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A10,Factors!$A$2:$A$21,0))</f>
         <v>Country of residence or incorporation</v>
       </c>
-      <c r="C10" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="19" t="n">
+      <c r="C10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A10,Factors!$A$2:$A$21,0))</f>
         <v>0.1</v>
       </c>
-      <c r="E10" s="28" t="n">
+      <c r="E10" s="27" t="n">
         <f aca="false">$D10*$C10</f>
         <v>0.1</v>
       </c>
-      <c r="F10" s="4" t="str">
+      <c r="F10" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A10)*(Levels!$C$2:$C$99=$C10),0),0))</f>
         <v>United Kingdom</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="21" t="str">
+      <c r="B11" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A11,Factors!$A$2:$A$21,0))</f>
         <v>Country of tax residence where different</v>
       </c>
-      <c r="C11" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="19" t="n">
+      <c r="C11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A11,Factors!$A$2:$A$21,0))</f>
         <v>0.05</v>
       </c>
-      <c r="E11" s="28" t="n">
+      <c r="E11" s="27" t="n">
         <f aca="false">$D11*$C11</f>
         <v>0.05</v>
       </c>
-      <c r="F11" s="4" t="str">
+      <c r="F11" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A11)*(Levels!$C$2:$C$99=$C11),0),0))</f>
         <v>No tax residence declared other than the United Kingdom</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="21" t="str">
+      <c r="B12" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A12,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty or payment corridor countries</v>
       </c>
-      <c r="C12" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="19" t="n">
+      <c r="C12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A12,Factors!$A$2:$A$21,0))</f>
         <v>0.1</v>
       </c>
-      <c r="E12" s="28" t="n">
+      <c r="E12" s="27" t="n">
         <f aca="false">$D12*$C12</f>
         <v>0.1</v>
       </c>
-      <c r="F12" s="4" t="str">
+      <c r="F12" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A12)*(Levels!$C$2:$C$99=$C12),0),0))</f>
         <v>United Kingdom only</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="21" t="str">
+      <c r="B13" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A13,Factors!$A$2:$A$21,0))</f>
         <v>Product type held</v>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A13,Factors!$A$2:$A$21,0))</f>
         <v>0.07</v>
       </c>
-      <c r="E13" s="28" t="n">
+      <c r="E13" s="27" t="n">
         <f aca="false">$D13*$C13</f>
         <v>0.28</v>
       </c>
-      <c r="F13" s="4" t="str">
+      <c r="F13" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A13)*(Levels!$C$2:$C$99=$C13),0),0))</f>
         <v>Business current account without cash handling or international payments</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="21" t="str">
+      <c r="B14" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A14,Factors!$A$2:$A$21,0))</f>
         <v>Cash functionality</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A14,Factors!$A$2:$A$21,0))</f>
         <v>0.05</v>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="27" t="n">
         <f aca="false">$D14*$C14</f>
         <v>0.25</v>
       </c>
-      <c r="F14" s="4" t="str">
+      <c r="F14" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A14)*(Levels!$C$2:$C$99=$C14),0),0))</f>
         <v>Cash deposits expected above GBP 10,000 a month, or use of a cash collection service</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="21" t="str">
+      <c r="B15" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A15,Factors!$A$2:$A$21,0))</f>
         <v>International payment functionality</v>
       </c>
-      <c r="C15" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="19" t="n">
+      <c r="C15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A15,Factors!$A$2:$A$21,0))</f>
         <v>0.05</v>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="27" t="n">
         <f aca="false">$D15*$C15</f>
         <v>0.05</v>
       </c>
-      <c r="F15" s="4" t="str">
+      <c r="F15" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A15)*(Levels!$C$2:$C$99=$C15),0),0))</f>
         <v>Not enabled on the account</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="21" t="str">
+      <c r="B16" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A16,Factors!$A$2:$A$21,0))</f>
         <v>Third-party access to the account</v>
       </c>
-      <c r="C16" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="19" t="n">
+      <c r="C16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A16,Factors!$A$2:$A$21,0))</f>
         <v>0.03</v>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="27" t="n">
         <f aca="false">$D16*$C16</f>
         <v>0.03</v>
       </c>
-      <c r="F16" s="4" t="str">
+      <c r="F16" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A16)*(Levels!$C$2:$C$99=$C16),0),0))</f>
         <v>Sole named party, no third-party access</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="21" t="str">
+      <c r="B17" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A17,Factors!$A$2:$A$21,0))</f>
         <v>Onboarding channel</v>
       </c>
-      <c r="C17" s="27" t="n">
+      <c r="C17" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A17,Factors!$A$2:$A$21,0))</f>
         <v>0.045</v>
       </c>
-      <c r="E17" s="28" t="n">
+      <c r="E17" s="27" t="n">
         <f aca="false">$D17*$C17</f>
         <v>0.135</v>
       </c>
-      <c r="F17" s="4" t="str">
+      <c r="F17" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A17)*(Levels!$C$2:$C$99=$C17),0),0))</f>
         <v>Digital application completed by the customer on the Bank's own app or website</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="21" t="str">
+      <c r="B18" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A18,Factors!$A$2:$A$21,0))</f>
         <v>Identity verification method</v>
       </c>
-      <c r="C18" s="27" t="n">
+      <c r="C18" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A18,Factors!$A$2:$A$21,0))</f>
         <v>0.035</v>
       </c>
-      <c r="E18" s="28" t="n">
+      <c r="E18" s="27" t="n">
         <f aca="false">$D18*$C18</f>
         <v>0.105</v>
       </c>
-      <c r="F18" s="4" t="str">
+      <c r="F18" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A18)*(Levels!$C$2:$C$99=$C18),0),0))</f>
         <v>Electronic verification returning two or more independent matching sources</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="21" t="str">
+      <c r="B19" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A19,Factors!$A$2:$A$21,0))</f>
         <v>Introduction source</v>
       </c>
-      <c r="C19" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="19" t="n">
+      <c r="C19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A19,Factors!$A$2:$A$21,0))</f>
         <v>0.02</v>
       </c>
-      <c r="E19" s="28" t="n">
+      <c r="E19" s="27" t="n">
         <f aca="false">$D19*$C19</f>
         <v>0.02</v>
       </c>
-      <c r="F19" s="4" t="str">
+      <c r="F19" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A19)*(Levels!$C$2:$C$99=$C19),0),0))</f>
         <v>Direct application by the customer</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="21" t="str">
+      <c r="B20" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A20,Factors!$A$2:$A$21,0))</f>
         <v>Expected turnover relative to declared income</v>
       </c>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A20,Factors!$A$2:$A$21,0))</f>
         <v>0.0375</v>
       </c>
-      <c r="E20" s="28" t="n">
+      <c r="E20" s="27" t="n">
         <f aca="false">$D20*$C20</f>
         <v>0.075</v>
       </c>
-      <c r="F20" s="4" t="str">
+      <c r="F20" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A20)*(Levels!$C$2:$C$99=$C20),0),0))</f>
         <v>Consistent with declared income or turnover, GBP 5,000 to GBP 25,000 a month</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="21" t="str">
+      <c r="B21" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A21,Factors!$A$2:$A$21,0))</f>
         <v>Expected cash proportion of credits</v>
       </c>
-      <c r="C21" s="27" t="n">
+      <c r="C21" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A21,Factors!$A$2:$A$21,0))</f>
         <v>0.045</v>
       </c>
-      <c r="E21" s="28" t="n">
+      <c r="E21" s="27" t="n">
         <f aca="false">$D21*$C21</f>
         <v>0.18</v>
       </c>
-      <c r="F21" s="4" t="str">
+      <c r="F21" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A21)*(Levels!$C$2:$C$99=$C21),0),0))</f>
         <v>Above 30% and up to 60% of expected monthly credits</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B22" s="21" t="str">
+      <c r="B22" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A22,Factors!$A$2:$A$21,0))</f>
         <v>Expected international proportion of value</v>
       </c>
-      <c r="C22" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="19" t="n">
+      <c r="C22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A22,Factors!$A$2:$A$21,0))</f>
         <v>0.03</v>
       </c>
-      <c r="E22" s="28" t="n">
+      <c r="E22" s="27" t="n">
         <f aca="false">$D22*$C22</f>
         <v>0.03</v>
       </c>
-      <c r="F22" s="4" t="str">
+      <c r="F22" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A22)*(Levels!$C$2:$C$99=$C22),0),0))</f>
         <v>No international activity declared</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B23" s="21" t="str">
+      <c r="B23" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A23,Factors!$A$2:$A$21,0))</f>
         <v>Expected counterparty profile</v>
       </c>
-      <c r="C23" s="27" t="n">
+      <c r="C23" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="19" t="n">
+      <c r="D23" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A23,Factors!$A$2:$A$21,0))</f>
         <v>0.0225</v>
       </c>
-      <c r="E23" s="28" t="n">
+      <c r="E23" s="27" t="n">
         <f aca="false">$D23*$C23</f>
         <v>0.0675</v>
       </c>
-      <c r="F23" s="4" t="str">
+      <c r="F23" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A23)*(Levels!$C$2:$C$99=$C23),0),0))</f>
         <v>A large number of individual counterparties, consistent with the stated business</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B24" s="21" t="str">
+      <c r="B24" s="20" t="str">
         <f aca="false">INDEX(Factors!$C$2:$C$21,MATCH($A24,Factors!$A$2:$A$21,0))</f>
         <v>Plausibility of the declared profile</v>
       </c>
-      <c r="C24" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="19" t="n">
+      <c r="C24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="18" t="n">
         <f aca="false">INDEX(Factors!$E$2:$E$21,MATCH($A24,Factors!$A$2:$A$21,0))</f>
         <v>0.015</v>
       </c>
-      <c r="E24" s="28" t="n">
+      <c r="E24" s="27" t="n">
         <f aca="false">$D24*$C24</f>
         <v>0.015</v>
       </c>
-      <c r="F24" s="4" t="str">
+      <c r="F24" s="3" t="str">
         <f aca="false">INDEX(Levels!$D$2:$D$99,MATCH(1,INDEX((Levels!$A$2:$A$99=$A24)*(Levels!$C$2:$C$99=$C24),0),0))</f>
         <v>Declared activity is consistent with every other item on file</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="I26" s="30" t="n">
+      <c r="I26" s="29" t="n">
         <f aca="false">SUM($E$5:$E$24)</f>
         <v>2.0725</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="I27" s="31" t="n">
+      <c r="I27" s="30" t="n">
         <f aca="false">ROUND($I26,2)</f>
         <v>2.07</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="I28" s="17" t="str">
+      <c r="I28" s="16" t="str">
         <f aca="false">IF($I27&lt;=2,"Low",IF($I27&lt;=3.49,"Medium","High"))</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="I29" s="27" t="s">
+      <c r="I29" s="26" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="I30" s="32" t="str">
+      <c r="I30" s="31" t="str">
         <f aca="false">IF($I29="Yes","High",$I28)</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G32" s="23" t="s">
+      <c r="G32" s="22" t="s">
         <v>277</v>
       </c>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5169,307 +5165,307 @@
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="33" t="s">
+      <c r="A5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="9" t="n">
         <f aca="false">ROUND(SUM(Categories!$C$2:$C$6),6)</f>
         <v>1</v>
       </c>
-      <c r="D5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="34" t="str">
+      <c r="D5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="33" t="str">
         <f aca="false">IF($C5=$D5,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <f aca="false">SUMPRODUCT(--(ROUND(Categories!$E$2:$E$6,6)&lt;&gt;1))</f>
         <v>0</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="34" t="str">
+      <c r="E6" s="33" t="str">
         <f aca="false">IF($C6=$D6,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="9" t="n">
         <f aca="false">ROUND(SUM(Factors!$E$2:$E$21),6)</f>
         <v>1</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="34" t="str">
+      <c r="D7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="33" t="str">
         <f aca="false">IF($C7=$D7,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="9" t="n">
         <f aca="false">SUMPRODUCT(--(COUNTIF(Factors!$A$2:$A$21,Factors!$A$2:$A$21)&gt;1))</f>
         <v>0</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="34" t="str">
+      <c r="E8" s="33" t="str">
         <f aca="false">IF($C8=$D8,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="9" t="n">
         <f aca="false">SUMPRODUCT(--(COUNTIF(Factors!$A$2:$A$21,Levels!$A$2:$A$99)=0))</f>
         <v>0</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="34" t="str">
+      <c r="E9" s="33" t="str">
         <f aca="false">IF($C9=$D9,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <f aca="false">SUMPRODUCT(--(COUNTIF(Levels!$A$2:$A$99,Factors!$A$2:$A$21)&lt;4))</f>
         <v>0</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="34" t="str">
+      <c r="E10" s="33" t="str">
         <f aca="false">IF($C10=$D10,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="9" t="n">
         <f aca="false">SUMPRODUCT(--((Levels!$C$2:$C$99&lt;1)+(Levels!$C$2:$C$99&gt;5)&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="34" t="str">
+      <c r="E11" s="33" t="str">
         <f aca="false">IF($C11=$D11,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="32" t="s">
         <v>292</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="9" t="n">
         <f aca="false">SUMPRODUCT(--(COUNTIFS(Levels!$A$2:$A$99,Levels!$A$2:$A$99,Levels!$C$2:$C$99,Levels!$C$2:$C$99)&gt;1))</f>
         <v>0</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="34" t="str">
+      <c r="E12" s="33" t="str">
         <f aca="false">IF($C12=$D12,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="32" t="s">
         <v>293</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="9" t="n">
         <f aca="false">SUMPRODUCT(--(Factors!$F$2:$F$21&lt;&gt;1))</f>
         <v>0</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="34" t="str">
+      <c r="E13" s="33" t="str">
         <f aca="false">IF($C13=$D13,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="32" t="s">
         <v>294</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="9" t="n">
         <f aca="false">SUMPRODUCT(--(Factors!$G$2:$G$21&lt;&gt;5))</f>
         <v>0</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="34" t="str">
+      <c r="E14" s="33" t="str">
         <f aca="false">IF($C14=$D14,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="32" t="s">
         <v>295</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="9" t="n">
         <f aca="false">ROUND(SUMPRODUCT(Factors!$E$2:$E$21,Factors!$F$2:$F$21),2)</f>
         <v>1</v>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="34" t="str">
+      <c r="D15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="33" t="str">
         <f aca="false">IF($C15=$D15,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="32" t="s">
         <v>296</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="9" t="n">
         <f aca="false">ROUND(SUMPRODUCT(Factors!$E$2:$E$21,Factors!$G$2:$G$21),2)</f>
         <v>5</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="34" t="str">
+      <c r="E16" s="33" t="str">
         <f aca="false">IF($C16=$D16,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="32" t="s">
         <v>297</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="28" t="n">
         <f aca="false">ROUND(SUM(Example!$E$5:$E$24),2)</f>
         <v>2.07</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="28" t="n">
         <v>2.07</v>
       </c>
-      <c r="E17" s="34" t="str">
+      <c r="E17" s="33" t="str">
         <f aca="false">IF($C17=$D17,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="E19" s="32" t="str">
+      <c r="E19" s="31" t="str">
         <f aca="false">IF(COUNTIF($E$5:$E$17,"CHECK")=0,"ALL OK","FIX")</f>
         <v>ALL OK</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="22" t="s">
         <v>299</v>
       </c>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/model/risk-factor-library.xlsx
+++ b/model/risk-factor-library.xlsx
@@ -460,7 +460,7 @@
     <t xml:space="preserve">Structure including a trust, a foundation, a nominee arrangement, or an entity incorporated outside the United Kingdom anywhere in the ownership chain</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3(d), fired on the whole level; see 5.3(d) and methodology 11.9</t>
+    <t xml:space="preserve">5.3(d), fired on the whole level; see 5.3(d) and methodology 11.9a</t>
   </si>
   <si>
     <t xml:space="preserve">Natural person; no beneficial ownership analysis required</t>
@@ -775,7 +775,7 @@
     <t xml:space="preserve">The customer is a money service business, a trust or company service provider, or a dealer in high-value goods.</t>
   </si>
   <si>
-    <t xml:space="preserve">The ownership structure includes nominee shareholders, bearer shares, or an entity incorporated in a jurisdiction with no accessible beneficial ownership register. Because level 5 of factor C1 covers trusts, nominee arrangements and overseas incorporation together, the recorded level cannot tell those apart; the escalator therefore fires on the whole of C1 level 5. That is deliberately conservative and it is the wrong way round: the fix is to split C1 level 5 so the condition can be evaluated, and that is a library change requiring approval (methodology 11.9).</t>
+    <t xml:space="preserve">The ownership structure includes nominee shareholders, bearer shares, or an entity incorporated in a jurisdiction with no accessible beneficial ownership register. Because level 5 of factor C1 covers trusts, nominee arrangements and overseas incorporation together, the recorded level cannot tell those apart; the escalator therefore fires on the whole of C1 level 5. That is deliberately conservative and it is the wrong way round: the fix is to split C1 level 5 so the condition can be evaluated, and that is a library change requiring approval (methodology 11.9a).</t>
   </si>
   <si>
     <t xml:space="preserve">Screening returns a confirmed adverse media match relating to financial crime, fraud, bribery, corruption or tax evasion.</t>
